--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BK6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
     <col width="10.7265625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -722,6 +722,21 @@
           <t>TTS26</t>
         </is>
       </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>S15S6</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>D31L6</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>D31M7</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -1452,6 +1467,196 @@
       </c>
       <c r="BH5" t="n">
         <v>158.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>102.31</v>
+      </c>
+      <c r="D6" t="n">
+        <v>142.515</v>
+      </c>
+      <c r="E6" t="n">
+        <v>105.069</v>
+      </c>
+      <c r="F6" t="n">
+        <v>113.653</v>
+      </c>
+      <c r="G6" t="n">
+        <v>103.369</v>
+      </c>
+      <c r="H6" t="n">
+        <v>120.49</v>
+      </c>
+      <c r="I6" t="n">
+        <v>108.985</v>
+      </c>
+      <c r="J6" t="n">
+        <v>123.29</v>
+      </c>
+      <c r="K6" t="n">
+        <v>116.549</v>
+      </c>
+      <c r="L6" t="n">
+        <v>139.85</v>
+      </c>
+      <c r="M6" t="n">
+        <v>126.89</v>
+      </c>
+      <c r="N6" t="n">
+        <v>119.89</v>
+      </c>
+      <c r="O6" t="n">
+        <v>122.9</v>
+      </c>
+      <c r="P6" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>109</v>
+      </c>
+      <c r="R6" t="n">
+        <v>388.05</v>
+      </c>
+      <c r="S6" t="n">
+        <v>162.25</v>
+      </c>
+      <c r="T6" t="n">
+        <v>285.75</v>
+      </c>
+      <c r="U6" t="n">
+        <v>210.2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>117</v>
+      </c>
+      <c r="W6" t="n">
+        <v>377.55</v>
+      </c>
+      <c r="X6" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>262.15</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>334.25</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>90.38</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>86.48999999999999</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>122.7</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>104</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>140780</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>139950</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>135000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>122700</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>63.97</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>78.77</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>81.39</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>73.61</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>65.43000000000001</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>65.17</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>72.18000000000001</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>93.98</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>159.7</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>100.379</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>140250</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>135800</v>
       </c>
     </row>
   </sheetData>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP9"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2338,6 +2338,211 @@
         <v>105.1</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>102.56</v>
+      </c>
+      <c r="D10" t="n">
+        <v>142.85</v>
+      </c>
+      <c r="E10" t="n">
+        <v>105.29</v>
+      </c>
+      <c r="F10" t="n">
+        <v>113.89</v>
+      </c>
+      <c r="G10" t="n">
+        <v>103.54</v>
+      </c>
+      <c r="H10" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>109.022</v>
+      </c>
+      <c r="J10" t="n">
+        <v>123.55</v>
+      </c>
+      <c r="K10" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>139.35</v>
+      </c>
+      <c r="M10" t="n">
+        <v>126.62</v>
+      </c>
+      <c r="N10" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>122.65</v>
+      </c>
+      <c r="P10" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>389.15</v>
+      </c>
+      <c r="S10" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>286.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>211.75</v>
+      </c>
+      <c r="V10" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>382</v>
+      </c>
+      <c r="X10" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>265.8</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>96.29000000000001</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>335.95</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>91.01000000000001</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>122.95</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>142800</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>142290</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>138290</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>126000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>95.84</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>64.39</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>64.41</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>79.48999999999999</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>74.58</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>65.81999999999999</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>65.62</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>81.98999999999999</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>85.76000000000001</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>76.31</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>73.38</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>89.65000000000001</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>160</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>159.4</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>142600</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>138600</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>101</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>105.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP11"/>
+  <dimension ref="A1:BP12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2745,6 +2745,208 @@
         <v>105.55</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>102.787</v>
+      </c>
+      <c r="D12" t="n">
+        <v>143.2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>105.595</v>
+      </c>
+      <c r="F12" t="n">
+        <v>114.15</v>
+      </c>
+      <c r="G12" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="H12" t="n">
+        <v>121.075</v>
+      </c>
+      <c r="I12" t="n">
+        <v>109.39</v>
+      </c>
+      <c r="J12" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>117.25</v>
+      </c>
+      <c r="L12" t="n">
+        <v>139.65</v>
+      </c>
+      <c r="M12" t="n">
+        <v>127.05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>99.12</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>390.2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>162.95</v>
+      </c>
+      <c r="T12" t="n">
+        <v>287.35</v>
+      </c>
+      <c r="U12" t="n">
+        <v>212.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>117.15</v>
+      </c>
+      <c r="W12" t="n">
+        <v>378.75</v>
+      </c>
+      <c r="X12" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>266.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>335.6</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>123.25</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>109</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>143550</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>143200</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>139350</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>126200</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>64.17</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>81.23999999999999</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>74</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>65.73</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>75.84999999999999</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>73.08</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>102</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>91.69</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>95.55</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>160.4</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>159.75</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>100.815</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>143500</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>140170</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>101</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>102</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>105.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP12"/>
+  <dimension ref="A1:BP13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2947,6 +2947,208 @@
         <v>105.9</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>102.836</v>
+      </c>
+      <c r="D13" t="n">
+        <v>143.283</v>
+      </c>
+      <c r="E13" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>114.369</v>
+      </c>
+      <c r="G13" t="n">
+        <v>104.025</v>
+      </c>
+      <c r="H13" t="n">
+        <v>121.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>117.25</v>
+      </c>
+      <c r="L13" t="n">
+        <v>140.349</v>
+      </c>
+      <c r="M13" t="n">
+        <v>127.388</v>
+      </c>
+      <c r="N13" t="n">
+        <v>120.35</v>
+      </c>
+      <c r="O13" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>390.6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>288</v>
+      </c>
+      <c r="U13" t="n">
+        <v>212.9</v>
+      </c>
+      <c r="V13" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>379.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>266.4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>88.15000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>143380</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>142600</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>139550</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>125480</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>95.69</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>64.14</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>93.43000000000001</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>64.11</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>79</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>74.18000000000001</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>65.59</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>81.29000000000001</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>75.79000000000001</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>102</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>102</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>94.55</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>160.6</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>101.12</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>143000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>140000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>105.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP16"/>
+  <dimension ref="A1:BU17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -762,6 +762,31 @@
           <t>GN49D</t>
         </is>
       </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>D31G6</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>TZVD8</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>TXMD8</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>TXMD9</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>TXMJ0</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -3747,6 +3772,220 @@
       </c>
       <c r="BP16" t="n">
         <v>105.85</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>143.75</v>
+      </c>
+      <c r="E17" t="n">
+        <v>105.999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>114.86</v>
+      </c>
+      <c r="G17" t="n">
+        <v>104.36</v>
+      </c>
+      <c r="H17" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>110.285</v>
+      </c>
+      <c r="J17" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>118.201</v>
+      </c>
+      <c r="L17" t="n">
+        <v>141.95</v>
+      </c>
+      <c r="M17" t="n">
+        <v>128.745</v>
+      </c>
+      <c r="N17" t="n">
+        <v>121.35</v>
+      </c>
+      <c r="O17" t="n">
+        <v>125</v>
+      </c>
+      <c r="P17" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>391.75</v>
+      </c>
+      <c r="S17" t="n">
+        <v>163.6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>288.25</v>
+      </c>
+      <c r="U17" t="n">
+        <v>213.25</v>
+      </c>
+      <c r="V17" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>382.35</v>
+      </c>
+      <c r="X17" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>88.31</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>111</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>103</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>142300</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>141510</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>138800</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>124500</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>65.12</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>64.56999999999999</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>81.05</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>83.31</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>75.47</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>66.22</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>83.86</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>88</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>78.43000000000001</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>75.14</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>92.08</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>161.05</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>101.48</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>142300</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>139800</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>104</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>112</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>142500</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>119500</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>79.59999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU20"/>
+  <dimension ref="A1:BU21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4660,6 +4660,220 @@
         <v>79.05</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>115.05</v>
+      </c>
+      <c r="G21" t="n">
+        <v>104.64</v>
+      </c>
+      <c r="H21" t="n">
+        <v>122</v>
+      </c>
+      <c r="I21" t="n">
+        <v>110.525</v>
+      </c>
+      <c r="J21" t="n">
+        <v>125.247</v>
+      </c>
+      <c r="K21" t="n">
+        <v>118.15</v>
+      </c>
+      <c r="L21" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>125</v>
+      </c>
+      <c r="P21" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="R21" t="n">
+        <v>392.95</v>
+      </c>
+      <c r="S21" t="n">
+        <v>163.55</v>
+      </c>
+      <c r="T21" t="n">
+        <v>287.45</v>
+      </c>
+      <c r="U21" t="n">
+        <v>213.25</v>
+      </c>
+      <c r="V21" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>380.4</v>
+      </c>
+      <c r="X21" t="n">
+        <v>102</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>267.4</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>340.95</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>124.14</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>116</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>145850</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>144550</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>141860</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>126100</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>64.84</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>64.42</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>80.95</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>84.05</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>66.01000000000001</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>87.91</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>78.04000000000001</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>75</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>161.65</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>160.95</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>101.72</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>145380</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>143600</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>111.35</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>145190</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>119900</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>89.19</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>82.73999999999999</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>79.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU22"/>
+  <dimension ref="A1:BU23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5088,6 +5088,220 @@
         <v>79.14</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>144.385</v>
+      </c>
+      <c r="E23" t="n">
+        <v>106.409</v>
+      </c>
+      <c r="F23" t="n">
+        <v>115.11</v>
+      </c>
+      <c r="G23" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="H23" t="n">
+        <v>121.95</v>
+      </c>
+      <c r="I23" t="n">
+        <v>110.46</v>
+      </c>
+      <c r="J23" t="n">
+        <v>124.556</v>
+      </c>
+      <c r="K23" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>141.519</v>
+      </c>
+      <c r="M23" t="n">
+        <v>128.65</v>
+      </c>
+      <c r="N23" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>124.52</v>
+      </c>
+      <c r="P23" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="R23" t="n">
+        <v>393.6</v>
+      </c>
+      <c r="S23" t="n">
+        <v>163.45</v>
+      </c>
+      <c r="T23" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>212.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="W23" t="n">
+        <v>378.4</v>
+      </c>
+      <c r="X23" t="n">
+        <v>102</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>266.6</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>338.55</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>124.369</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>105</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>146850</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>146030</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>143500</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>126200</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>96.98999999999999</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>64.38</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>81.17</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>83.86</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>75.98999999999999</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>84.19</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>87.72</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>78.02</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>94.20999999999999</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>161.85</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>161</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>101.82</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>146580</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>144400</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>105</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>146750</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>120500</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>79.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU23"/>
+  <dimension ref="A1:BU24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5302,6 +5302,220 @@
         <v>79.09</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>144.47</v>
+      </c>
+      <c r="E24" t="n">
+        <v>106.49</v>
+      </c>
+      <c r="F24" t="n">
+        <v>115.14</v>
+      </c>
+      <c r="G24" t="n">
+        <v>104.77</v>
+      </c>
+      <c r="H24" t="n">
+        <v>122.15</v>
+      </c>
+      <c r="I24" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>124.601</v>
+      </c>
+      <c r="K24" t="n">
+        <v>117.847</v>
+      </c>
+      <c r="L24" t="n">
+        <v>141.35</v>
+      </c>
+      <c r="M24" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>121.524</v>
+      </c>
+      <c r="O24" t="n">
+        <v>124.469</v>
+      </c>
+      <c r="P24" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="R24" t="n">
+        <v>393.8</v>
+      </c>
+      <c r="S24" t="n">
+        <v>163.6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>287.35</v>
+      </c>
+      <c r="U24" t="n">
+        <v>211.8</v>
+      </c>
+      <c r="V24" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="W24" t="n">
+        <v>376.6</v>
+      </c>
+      <c r="X24" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>266</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>337.75</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>124.34</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>115.85</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>105</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>147500</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>147450</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>143690</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>126300</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>64.34</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>81.43000000000001</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>84.23999999999999</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>66.19</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>66.04000000000001</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>84.34999999999999</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>102</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>89.05</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>161.15</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>147500</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>144700</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>146510</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>121500</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>82.95</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>79.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU24"/>
+  <dimension ref="A1:BU25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5516,6 +5516,220 @@
         <v>79.63</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>144.52</v>
+      </c>
+      <c r="E25" t="n">
+        <v>106.48</v>
+      </c>
+      <c r="F25" t="n">
+        <v>115.17</v>
+      </c>
+      <c r="G25" t="n">
+        <v>104.72</v>
+      </c>
+      <c r="H25" t="n">
+        <v>121.82</v>
+      </c>
+      <c r="I25" t="n">
+        <v>110.33</v>
+      </c>
+      <c r="J25" t="n">
+        <v>125.049</v>
+      </c>
+      <c r="K25" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>141.2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="N25" t="n">
+        <v>121.79</v>
+      </c>
+      <c r="O25" t="n">
+        <v>122.95</v>
+      </c>
+      <c r="P25" t="n">
+        <v>99.56</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="R25" t="n">
+        <v>393.8</v>
+      </c>
+      <c r="S25" t="n">
+        <v>163.35</v>
+      </c>
+      <c r="T25" t="n">
+        <v>287</v>
+      </c>
+      <c r="U25" t="n">
+        <v>211.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>117</v>
+      </c>
+      <c r="W25" t="n">
+        <v>375.6</v>
+      </c>
+      <c r="X25" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>265.6</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>87.58</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>124.42</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>105</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>103</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>147290</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>146700</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>143790</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>126390</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>64.42</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>81.95</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>76.78</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>66.06999999999999</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>66.09</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>84.55</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>88.04000000000001</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>78.55</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>75.59</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>92.27</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>92.34999999999999</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>94.45</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>161.95</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>161.2</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>101.69</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>146600</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>144260</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>147000</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>120000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>82.44</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>79.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY28"/>
+  <dimension ref="A1:BY29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6380,6 +6380,220 @@
         <v>101.7</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>106.97</v>
+      </c>
+      <c r="F29" t="n">
+        <v>115.749</v>
+      </c>
+      <c r="G29" t="n">
+        <v>105.33</v>
+      </c>
+      <c r="H29" t="n">
+        <v>122.75</v>
+      </c>
+      <c r="I29" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="J29" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="L29" t="n">
+        <v>143</v>
+      </c>
+      <c r="M29" t="n">
+        <v>130.29</v>
+      </c>
+      <c r="N29" t="n">
+        <v>123.7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="S29" t="n">
+        <v>164.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>288.65</v>
+      </c>
+      <c r="U29" t="n">
+        <v>212.9</v>
+      </c>
+      <c r="V29" t="n">
+        <v>117.85</v>
+      </c>
+      <c r="W29" t="n">
+        <v>377</v>
+      </c>
+      <c r="X29" t="n">
+        <v>102</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>266.6</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>338</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>91.76000000000001</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>88</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>125.099</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>116.15</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>146700</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>146800</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>127600</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>64.18000000000001</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>84.38</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>66.03</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>84.95</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>79.42</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>92.69</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>92.62</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>162.15</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>147600</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>147300</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>101</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>147200</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>122200</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>80.15000000000001</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>100.79</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>92.34999999999999</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>82.09</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>101.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY30"/>
+  <dimension ref="A1:BY31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6808,6 +6808,220 @@
         <v>101.7</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="F31" t="n">
+        <v>116.09</v>
+      </c>
+      <c r="G31" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="H31" t="n">
+        <v>123.15</v>
+      </c>
+      <c r="I31" t="n">
+        <v>111.62</v>
+      </c>
+      <c r="J31" t="n">
+        <v>126.06</v>
+      </c>
+      <c r="K31" t="n">
+        <v>119.05</v>
+      </c>
+      <c r="L31" t="n">
+        <v>144</v>
+      </c>
+      <c r="M31" t="n">
+        <v>131</v>
+      </c>
+      <c r="N31" t="n">
+        <v>123.61</v>
+      </c>
+      <c r="O31" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="P31" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="S31" t="n">
+        <v>164.85</v>
+      </c>
+      <c r="T31" t="n">
+        <v>289.95</v>
+      </c>
+      <c r="U31" t="n">
+        <v>214</v>
+      </c>
+      <c r="V31" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="W31" t="n">
+        <v>380.45</v>
+      </c>
+      <c r="X31" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>341</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>88.23999999999999</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>125.45</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>116.55</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>111</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>146950</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>145350</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>127600</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>64.98</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>81.88</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>78.55</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>66.17</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>66.09</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>85.31999999999999</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>89.09</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>102</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>92.73</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>162.6</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>102.73</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>147850</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>146700</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>101</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>147700</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>122200</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>83.84</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>80.94</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>101.229</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>82.65000000000001</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>102.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY32"/>
+  <dimension ref="A1:BY33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7236,6 +7236,220 @@
         <v>102.5</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>107.379</v>
+      </c>
+      <c r="F33" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>105.656</v>
+      </c>
+      <c r="H33" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>111.73</v>
+      </c>
+      <c r="J33" t="n">
+        <v>126.35</v>
+      </c>
+      <c r="K33" t="n">
+        <v>119.11</v>
+      </c>
+      <c r="L33" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>131.31</v>
+      </c>
+      <c r="N33" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="O33" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>165.2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>290.45</v>
+      </c>
+      <c r="U33" t="n">
+        <v>214.7</v>
+      </c>
+      <c r="V33" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="W33" t="n">
+        <v>383.3</v>
+      </c>
+      <c r="X33" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>268.85</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>116.65</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>106</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>146740</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>146000</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>128000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>97.31</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>65.47</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>85</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>79</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>66.33</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>85.29000000000001</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>76</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>102</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>93.19</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>162.7</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>102.836</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>147800</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>145950</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>148350</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>122900</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>84.20999999999999</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>81.43000000000001</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>101.44</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>93.44</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>83.15000000000001</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>102.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY33"/>
+  <dimension ref="A1:BY34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7450,6 +7450,220 @@
         <v>102.8</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>107.66</v>
+      </c>
+      <c r="F34" t="n">
+        <v>116.45</v>
+      </c>
+      <c r="G34" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="H34" t="n">
+        <v>123.36</v>
+      </c>
+      <c r="I34" t="n">
+        <v>111.94</v>
+      </c>
+      <c r="J34" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>119.548</v>
+      </c>
+      <c r="L34" t="n">
+        <v>144</v>
+      </c>
+      <c r="M34" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>124.701</v>
+      </c>
+      <c r="O34" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="P34" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="S34" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>291.2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>215.2</v>
+      </c>
+      <c r="V34" t="n">
+        <v>118</v>
+      </c>
+      <c r="W34" t="n">
+        <v>384</v>
+      </c>
+      <c r="X34" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>269.2</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>343.35</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>89.39</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>125.93</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>117.05</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>147400</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>145400</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>128300</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>79.98</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>76.87</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>57.43</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>82.95</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>86.78</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>77.68000000000001</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>71.62</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>92.78</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>147940</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>145700</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>147740</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>123000</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>84.34</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>81.37</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>102.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY34"/>
+  <dimension ref="A1:BY35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7664,6 +7664,220 @@
         <v>102.9</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>107.66</v>
+      </c>
+      <c r="F35" t="n">
+        <v>116.45</v>
+      </c>
+      <c r="G35" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="H35" t="n">
+        <v>123.36</v>
+      </c>
+      <c r="I35" t="n">
+        <v>111.94</v>
+      </c>
+      <c r="J35" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>119.548</v>
+      </c>
+      <c r="L35" t="n">
+        <v>144</v>
+      </c>
+      <c r="M35" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>124.701</v>
+      </c>
+      <c r="O35" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="P35" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="S35" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>291.2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>215.2</v>
+      </c>
+      <c r="V35" t="n">
+        <v>118</v>
+      </c>
+      <c r="W35" t="n">
+        <v>384</v>
+      </c>
+      <c r="X35" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>269.2</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>343.35</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>89.39</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>125.93</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>117.05</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>147400</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>145400</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>128300</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>79.98</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>76.87</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>57.43</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>82.95</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>86.78</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>77.68000000000001</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>71.62</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>92.78</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>147940</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>145700</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>147740</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>123000</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>84.34</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>81.37</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>102.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY35"/>
+  <dimension ref="A1:BY36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7878,6 +7878,220 @@
         <v>102.9</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>107.69</v>
+      </c>
+      <c r="F36" t="n">
+        <v>116.747</v>
+      </c>
+      <c r="G36" t="n">
+        <v>106.198</v>
+      </c>
+      <c r="H36" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>112.005</v>
+      </c>
+      <c r="J36" t="n">
+        <v>127</v>
+      </c>
+      <c r="K36" t="n">
+        <v>119.85</v>
+      </c>
+      <c r="L36" t="n">
+        <v>144.4</v>
+      </c>
+      <c r="M36" t="n">
+        <v>131.55</v>
+      </c>
+      <c r="N36" t="n">
+        <v>126</v>
+      </c>
+      <c r="O36" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="P36" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="S36" t="n">
+        <v>165</v>
+      </c>
+      <c r="T36" t="n">
+        <v>290.55</v>
+      </c>
+      <c r="U36" t="n">
+        <v>216.05</v>
+      </c>
+      <c r="V36" t="n">
+        <v>118</v>
+      </c>
+      <c r="W36" t="n">
+        <v>383.8</v>
+      </c>
+      <c r="X36" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>269.45</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>98</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>343.25</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>92.95</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>88.86</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>125.87</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>118.95</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>147350</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>145500</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>128690</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>80.48999999999999</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>55.66</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>83.23999999999999</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>86.76000000000001</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>78.09</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>93.11</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>92.34999999999999</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>162.3</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>103.569</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>147800</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>146470</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>147900</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>123460</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>85</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>81.88</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>97.65000000000001</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY37"/>
+  <dimension ref="A1:BY38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8306,6 +8306,220 @@
         <v>102.9</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>107.79</v>
+      </c>
+      <c r="F38" t="n">
+        <v>116.63</v>
+      </c>
+      <c r="G38" t="n">
+        <v>106.11</v>
+      </c>
+      <c r="H38" t="n">
+        <v>123.55</v>
+      </c>
+      <c r="I38" t="n">
+        <v>112.04</v>
+      </c>
+      <c r="J38" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="K38" t="n">
+        <v>119.262</v>
+      </c>
+      <c r="L38" t="n">
+        <v>144.05</v>
+      </c>
+      <c r="M38" t="n">
+        <v>131.55</v>
+      </c>
+      <c r="N38" t="n">
+        <v>124.439</v>
+      </c>
+      <c r="O38" t="n">
+        <v>126.899</v>
+      </c>
+      <c r="P38" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="S38" t="n">
+        <v>165.7</v>
+      </c>
+      <c r="T38" t="n">
+        <v>291.65</v>
+      </c>
+      <c r="U38" t="n">
+        <v>215.45</v>
+      </c>
+      <c r="V38" t="n">
+        <v>118.95</v>
+      </c>
+      <c r="W38" t="n">
+        <v>384.45</v>
+      </c>
+      <c r="X38" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>268.45</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>97</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>343.1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>93</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>126.03</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>111.35</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>106</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>145600</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>143500</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>126000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>97.48999999999999</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>80.45</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>76.98</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>78</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>71.34999999999999</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>92.61</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>163.4</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>103.13</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>146150</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>145050</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>146000</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>121400</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="BV38" t="n">
+        <v>101.665</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY38"/>
+  <dimension ref="A1:BY39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8520,6 +8520,220 @@
         <v>103</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>107.864</v>
+      </c>
+      <c r="F39" t="n">
+        <v>116.73</v>
+      </c>
+      <c r="G39" t="n">
+        <v>106.209</v>
+      </c>
+      <c r="H39" t="n">
+        <v>123.7</v>
+      </c>
+      <c r="I39" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="J39" t="n">
+        <v>126.95</v>
+      </c>
+      <c r="K39" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="L39" t="n">
+        <v>144.35</v>
+      </c>
+      <c r="M39" t="n">
+        <v>131.7</v>
+      </c>
+      <c r="N39" t="n">
+        <v>124.45</v>
+      </c>
+      <c r="O39" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="P39" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>113</v>
+      </c>
+      <c r="S39" t="n">
+        <v>165.8</v>
+      </c>
+      <c r="T39" t="n">
+        <v>292</v>
+      </c>
+      <c r="U39" t="n">
+        <v>215.6</v>
+      </c>
+      <c r="V39" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>384.75</v>
+      </c>
+      <c r="X39" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>268.3</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>96.70999999999999</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>344.25</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>93.27</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>126.14</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>111.35</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>146030</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>144400</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>126490</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>103</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>83.54000000000001</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>76.88</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>55.39</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>87.72</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>78.23</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>72.11</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>92.66</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>97</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>90.76000000000001</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>163.35</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>146500</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>145250</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>106</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>146400</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>120600</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>92</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>84.89</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>101.726</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>83.95</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>103.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY40"/>
+  <dimension ref="A1:CA41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -807,6 +807,16 @@
           <t>TML27</t>
         </is>
       </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>D10Y7</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>AO29D</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -8943,6 +8953,223 @@
       </c>
       <c r="BY40" t="n">
         <v>103.3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>106.48</v>
+      </c>
+      <c r="H41" t="n">
+        <v>124</v>
+      </c>
+      <c r="I41" t="n">
+        <v>112.599</v>
+      </c>
+      <c r="J41" t="n">
+        <v>127.25</v>
+      </c>
+      <c r="K41" t="n">
+        <v>119.64</v>
+      </c>
+      <c r="L41" t="n">
+        <v>144.34</v>
+      </c>
+      <c r="M41" t="n">
+        <v>131.72</v>
+      </c>
+      <c r="N41" t="n">
+        <v>124.45</v>
+      </c>
+      <c r="O41" t="n">
+        <v>126.19</v>
+      </c>
+      <c r="P41" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="S41" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="T41" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="U41" t="n">
+        <v>215.7</v>
+      </c>
+      <c r="V41" t="n">
+        <v>119.45</v>
+      </c>
+      <c r="W41" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="X41" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>268.7</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>344.05</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>89.89</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>126.53</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>146550</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>144700</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>126840</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>97.89</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>97.15000000000002</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>80.81999999999999</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>83.64</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>76.91</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>57.98999999999999</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>77.98</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>72.06999999999999</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>93.09</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>163.8</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>103.59</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>147290</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>145540</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>104</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>105</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>108</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>146750</v>
+      </c>
+      <c r="BR41" t="n">
+        <v>120500</v>
+      </c>
+      <c r="BS41" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="BT41" t="n">
+        <v>85.09</v>
+      </c>
+      <c r="BU41" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="BV41" t="n">
+        <v>102.06</v>
+      </c>
+      <c r="BW41" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="BX41" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="BY41" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="BZ41" t="n">
+        <v>146600</v>
+      </c>
+      <c r="CA41" t="n">
+        <v>94.64000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA41"/>
+  <dimension ref="A1:CA42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9172,6 +9172,223 @@
         <v>94.64000000000001</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>117.06</v>
+      </c>
+      <c r="G42" t="n">
+        <v>106.535</v>
+      </c>
+      <c r="H42" t="n">
+        <v>124.08</v>
+      </c>
+      <c r="I42" t="n">
+        <v>112.599</v>
+      </c>
+      <c r="J42" t="n">
+        <v>127.369</v>
+      </c>
+      <c r="K42" t="n">
+        <v>119.679</v>
+      </c>
+      <c r="L42" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="N42" t="n">
+        <v>124.37</v>
+      </c>
+      <c r="O42" t="n">
+        <v>126</v>
+      </c>
+      <c r="P42" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>166.4</v>
+      </c>
+      <c r="T42" t="n">
+        <v>292.8</v>
+      </c>
+      <c r="U42" t="n">
+        <v>216.05</v>
+      </c>
+      <c r="V42" t="n">
+        <v>119.05</v>
+      </c>
+      <c r="W42" t="n">
+        <v>385.25</v>
+      </c>
+      <c r="X42" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>344.85</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>104</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>146490</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>144250</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>126650</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>97.45999999999999</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>56.42</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>58.15</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>78.23999999999999</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>94</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>164.1</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>103.68</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>147590</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>144160</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>103</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>146780</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>120500</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>92</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="BU42" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="BV42" t="n">
+        <v>102.119</v>
+      </c>
+      <c r="BW42" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="BY42" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="BZ42" t="n">
+        <v>146420</v>
+      </c>
+      <c r="CA42" t="n">
+        <v>94.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA42"/>
+  <dimension ref="A1:CA43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9389,6 +9389,223 @@
         <v>94.98</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>117.139</v>
+      </c>
+      <c r="G43" t="n">
+        <v>106.57</v>
+      </c>
+      <c r="H43" t="n">
+        <v>124.13</v>
+      </c>
+      <c r="I43" t="n">
+        <v>112.625</v>
+      </c>
+      <c r="J43" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>119.643</v>
+      </c>
+      <c r="L43" t="n">
+        <v>144</v>
+      </c>
+      <c r="M43" t="n">
+        <v>131.62</v>
+      </c>
+      <c r="N43" t="n">
+        <v>124.29</v>
+      </c>
+      <c r="O43" t="n">
+        <v>125.88</v>
+      </c>
+      <c r="P43" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="S43" t="n">
+        <v>166.65</v>
+      </c>
+      <c r="T43" t="n">
+        <v>293.1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>216.35</v>
+      </c>
+      <c r="V43" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>385.2</v>
+      </c>
+      <c r="X43" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>270.4</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>344.9</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>89.89</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>107</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>146250</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>144500</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>126300</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>103</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>98.16</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>55.84</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>83.39</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>78.12</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>93.28</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>92.69</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>164.25</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>103.68</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>147260</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>144200</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>146420</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>120200</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>92</v>
+      </c>
+      <c r="BT43" t="n">
+        <v>85.02</v>
+      </c>
+      <c r="BU43" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="BV43" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="BZ43" t="n">
+        <v>146600</v>
+      </c>
+      <c r="CA43" t="n">
+        <v>95.06999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA43"/>
+  <dimension ref="A1:CA44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9606,6 +9606,223 @@
         <v>95.06999999999999</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>117.154</v>
+      </c>
+      <c r="G44" t="n">
+        <v>106.592</v>
+      </c>
+      <c r="H44" t="n">
+        <v>124.18</v>
+      </c>
+      <c r="I44" t="n">
+        <v>112.63</v>
+      </c>
+      <c r="J44" t="n">
+        <v>127.25</v>
+      </c>
+      <c r="K44" t="n">
+        <v>119.65</v>
+      </c>
+      <c r="L44" t="n">
+        <v>144.1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>131.498</v>
+      </c>
+      <c r="N44" t="n">
+        <v>124.099</v>
+      </c>
+      <c r="O44" t="n">
+        <v>125.65</v>
+      </c>
+      <c r="P44" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="S44" t="n">
+        <v>166.75</v>
+      </c>
+      <c r="T44" t="n">
+        <v>293.35</v>
+      </c>
+      <c r="U44" t="n">
+        <v>216.45</v>
+      </c>
+      <c r="V44" t="n">
+        <v>119.6</v>
+      </c>
+      <c r="W44" t="n">
+        <v>386.45</v>
+      </c>
+      <c r="X44" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>270.85</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>345.2</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>90.14</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>146900</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>144390</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>126290</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>98.59</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>55.38000000000001</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>97.08</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>81.34</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>83.89</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>56</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>58.42</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>72.09</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>93.64999999999999</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>91.04000000000001</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>164.35</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>103.73</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>147450</v>
+      </c>
+      <c r="BK44" t="n">
+        <v>144800</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>146900</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>120100</v>
+      </c>
+      <c r="BS44" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="BT44" t="n">
+        <v>85</v>
+      </c>
+      <c r="BU44" t="n">
+        <v>82.05</v>
+      </c>
+      <c r="BV44" t="n">
+        <v>102.115</v>
+      </c>
+      <c r="BW44" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="BX44" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="BY44" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="BZ44" t="n">
+        <v>146600</v>
+      </c>
+      <c r="CA44" t="n">
+        <v>95.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA44"/>
+  <dimension ref="A1:CA45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9823,6 +9823,223 @@
         <v>95.2</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>106.64</v>
+      </c>
+      <c r="H45" t="n">
+        <v>124.19</v>
+      </c>
+      <c r="I45" t="n">
+        <v>112.601</v>
+      </c>
+      <c r="J45" t="n">
+        <v>127.45</v>
+      </c>
+      <c r="K45" t="n">
+        <v>119.65</v>
+      </c>
+      <c r="L45" t="n">
+        <v>144.139</v>
+      </c>
+      <c r="M45" t="n">
+        <v>131.28</v>
+      </c>
+      <c r="N45" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="O45" t="n">
+        <v>125.35</v>
+      </c>
+      <c r="P45" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>113</v>
+      </c>
+      <c r="S45" t="n">
+        <v>166.85</v>
+      </c>
+      <c r="T45" t="n">
+        <v>293.65</v>
+      </c>
+      <c r="U45" t="n">
+        <v>216.75</v>
+      </c>
+      <c r="V45" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="W45" t="n">
+        <v>386.6</v>
+      </c>
+      <c r="X45" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>270.75</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>97.65000000000001</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>345.55</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>93.88</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>127</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>147400</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>145400</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>126590</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>98.27</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>83.15000000000001</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>55.78999999999998</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>82.44</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>71.06999999999999</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>103.72</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>148350</v>
+      </c>
+      <c r="BK45" t="n">
+        <v>144990</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>114</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="BQ45" t="n">
+        <v>147640</v>
+      </c>
+      <c r="BR45" t="n">
+        <v>120410</v>
+      </c>
+      <c r="BS45" t="n">
+        <v>92.04000000000001</v>
+      </c>
+      <c r="BT45" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="BU45" t="n">
+        <v>81.84999999999999</v>
+      </c>
+      <c r="BV45" t="n">
+        <v>102.145</v>
+      </c>
+      <c r="BW45" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="BX45" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="BY45" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="BZ45" t="n">
+        <v>146600</v>
+      </c>
+      <c r="CA45" t="n">
+        <v>94.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA45"/>
+  <dimension ref="A1:CA46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10040,6 +10040,223 @@
         <v>94.95</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>117.43</v>
+      </c>
+      <c r="G46" t="n">
+        <v>106.864</v>
+      </c>
+      <c r="H46" t="n">
+        <v>124.388</v>
+      </c>
+      <c r="I46" t="n">
+        <v>112.87</v>
+      </c>
+      <c r="J46" t="n">
+        <v>127.6</v>
+      </c>
+      <c r="K46" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="L46" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>131.45</v>
+      </c>
+      <c r="N46" t="n">
+        <v>123.85</v>
+      </c>
+      <c r="O46" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="P46" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>167.15</v>
+      </c>
+      <c r="T46" t="n">
+        <v>294.2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>217.25</v>
+      </c>
+      <c r="V46" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="W46" t="n">
+        <v>387.45</v>
+      </c>
+      <c r="X46" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>97.95</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>346.65</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>90.04000000000001</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>127.075</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>117.85</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>148010</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>146540</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>126860</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>98.64999999999999</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>80</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>82.95999999999999</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>55.99000000000001</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>86.23999999999999</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>77.09</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>93.51000000000001</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>93.19</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>164.85</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>103.97</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>149200</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>145800</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>103</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>105</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>148430</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>121190</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="BT46" t="n">
+        <v>85.06</v>
+      </c>
+      <c r="BU46" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>94.34999999999999</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>84.84999999999999</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>146600</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>95.16999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG45"/>
+  <dimension ref="A1:GG46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -21390,6 +21390,529 @@
         <v>103.9</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>117.43</v>
+      </c>
+      <c r="G46" t="n">
+        <v>106.864</v>
+      </c>
+      <c r="H46" t="n">
+        <v>124.388</v>
+      </c>
+      <c r="I46" t="n">
+        <v>112.87</v>
+      </c>
+      <c r="J46" t="n">
+        <v>127.6</v>
+      </c>
+      <c r="K46" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="L46" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>131.45</v>
+      </c>
+      <c r="N46" t="n">
+        <v>123.85</v>
+      </c>
+      <c r="O46" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="P46" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>167.15</v>
+      </c>
+      <c r="T46" t="n">
+        <v>294.2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>217.25</v>
+      </c>
+      <c r="V46" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="W46" t="n">
+        <v>387.45</v>
+      </c>
+      <c r="X46" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>97.95</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>346.65</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>90.04000000000001</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>127.075</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>117.85</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>148010</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>146540</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>126860</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>98.64999999999999</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>80</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>82.95999999999999</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>55.99000000000001</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>86.23999999999999</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>77.09</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>93.51000000000001</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>93.19</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>164.85</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>103.97</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>149200</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>145800</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>103</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>105</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>148430</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>121190</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="BT46" t="n">
+        <v>85.06</v>
+      </c>
+      <c r="BU46" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>94.34999999999999</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>84.84999999999999</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>146600</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>95.16999999999999</v>
+      </c>
+      <c r="CB46" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="CC46" t="n">
+        <v>121.16</v>
+      </c>
+      <c r="CE46" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="CF46" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="CG46" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="CH46" t="n">
+        <v>32014.25</v>
+      </c>
+      <c r="CM46" t="n">
+        <v>59960</v>
+      </c>
+      <c r="CN46" t="n">
+        <v>29754.62</v>
+      </c>
+      <c r="CQ46" t="n">
+        <v>73500</v>
+      </c>
+      <c r="CS46" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="CT46" t="n">
+        <v>47281.86</v>
+      </c>
+      <c r="CU46" t="n">
+        <v>41575.111</v>
+      </c>
+      <c r="CV46" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="CW46" t="n">
+        <v>36128.597</v>
+      </c>
+      <c r="CX46" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="CY46" t="n">
+        <v>162680</v>
+      </c>
+      <c r="CZ46" t="n">
+        <v>169900</v>
+      </c>
+      <c r="DA46" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="DB46" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="DC46" t="n">
+        <v>172990</v>
+      </c>
+      <c r="DD46" t="n">
+        <v>104</v>
+      </c>
+      <c r="DE46" t="n">
+        <v>79.84999999999999</v>
+      </c>
+      <c r="DF46" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="DG46" t="n">
+        <v>124490</v>
+      </c>
+      <c r="DH46" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="DI46" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="DJ46" t="n">
+        <v>109</v>
+      </c>
+      <c r="DK46" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="DL46" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="DM46" t="n">
+        <v>85.15000000000001</v>
+      </c>
+      <c r="DN46" t="n">
+        <v>51.45000000000001</v>
+      </c>
+      <c r="DO46" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="DP46" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="DQ46" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="DR46" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="DS46" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="DT46" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DU46" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="DV46" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="DW46" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="DX46" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="DY46" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="DZ46" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="EA46" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="EB46" t="n">
+        <v>110.85</v>
+      </c>
+      <c r="EC46" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="ED46" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="EE46" t="n">
+        <v>109</v>
+      </c>
+      <c r="EF46" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="EG46" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="EH46" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="EI46" t="n">
+        <v>109</v>
+      </c>
+      <c r="EJ46" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="EK46" t="n">
+        <v>111</v>
+      </c>
+      <c r="EL46" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EM46" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="EN46" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EO46" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="EP46" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="EQ46" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="ER46" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="ES46" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="ET46" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="EU46" t="n">
+        <v>106</v>
+      </c>
+      <c r="EV46" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EW46" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="EX46" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="EY46" t="n">
+        <v>112.15</v>
+      </c>
+      <c r="EZ46" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="FA46" t="n">
+        <v>104</v>
+      </c>
+      <c r="FB46" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="FC46" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="FD46" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="FE46" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="FF46" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="FG46" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="FH46" t="n">
+        <v>103</v>
+      </c>
+      <c r="FI46" t="n">
+        <v>105</v>
+      </c>
+      <c r="FJ46" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="FK46" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="FL46" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="FM46" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="FN46" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="FO46" t="n">
+        <v>103</v>
+      </c>
+      <c r="FP46" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="FQ46" t="n">
+        <v>102</v>
+      </c>
+      <c r="FR46" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="FS46" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="FT46" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="FU46" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="FV46" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="FW46" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="FX46" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="FY46" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="FZ46" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="GA46" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="GB46" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="GC46" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="GD46" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="GE46" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="GF46" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="GG46" t="n">
+        <v>100.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA46"/>
+  <dimension ref="A1:CA47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10257,6 +10257,223 @@
         <v>95.16999999999999</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>117.484</v>
+      </c>
+      <c r="G47" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="H47" t="n">
+        <v>124.48</v>
+      </c>
+      <c r="I47" t="n">
+        <v>112.882</v>
+      </c>
+      <c r="J47" t="n">
+        <v>127.53</v>
+      </c>
+      <c r="K47" t="n">
+        <v>119.931</v>
+      </c>
+      <c r="L47" t="n">
+        <v>144.519</v>
+      </c>
+      <c r="M47" t="n">
+        <v>131.425</v>
+      </c>
+      <c r="N47" t="n">
+        <v>124.05</v>
+      </c>
+      <c r="O47" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="P47" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="S47" t="n">
+        <v>167.3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>294.4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="V47" t="n">
+        <v>120</v>
+      </c>
+      <c r="W47" t="n">
+        <v>388</v>
+      </c>
+      <c r="X47" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>271.15</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>98.13</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>347.05</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>89.77</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>127.14</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>148490</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>146250</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>127120</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>55.24</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>96.93000000000001</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>56.89999999999999</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>79.87</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>82.84999999999999</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>75.45999999999999</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>86.17</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>77.12</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>70.91</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>103</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>93.45</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>103.96</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>149350</v>
+      </c>
+      <c r="BK47" t="n">
+        <v>146500</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>148520</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>121250</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="BT47" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="BU47" t="n">
+        <v>82.12</v>
+      </c>
+      <c r="BV47" t="n">
+        <v>102.38</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>84.81</v>
+      </c>
+      <c r="BY47" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="BZ47" t="n">
+        <v>146600</v>
+      </c>
+      <c r="CA47" t="n">
+        <v>95.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG46"/>
+  <dimension ref="A1:GG47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -21913,6 +21913,529 @@
         <v>100.05</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>117.484</v>
+      </c>
+      <c r="G47" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="H47" t="n">
+        <v>124.48</v>
+      </c>
+      <c r="I47" t="n">
+        <v>112.882</v>
+      </c>
+      <c r="J47" t="n">
+        <v>127.53</v>
+      </c>
+      <c r="K47" t="n">
+        <v>119.931</v>
+      </c>
+      <c r="L47" t="n">
+        <v>144.519</v>
+      </c>
+      <c r="M47" t="n">
+        <v>131.425</v>
+      </c>
+      <c r="N47" t="n">
+        <v>124.05</v>
+      </c>
+      <c r="O47" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="P47" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="S47" t="n">
+        <v>167.3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>294.4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="V47" t="n">
+        <v>120</v>
+      </c>
+      <c r="W47" t="n">
+        <v>388</v>
+      </c>
+      <c r="X47" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>271.15</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>98.13</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>347.05</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>89.77</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>127.14</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>148490</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>146250</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>127120</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>55.24</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>96.93000000000001</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>56.89999999999999</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>79.87</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>82.84999999999999</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>75.45999999999999</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>86.17</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>77.12</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>70.91</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>103</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>93.45</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>103.96</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>149350</v>
+      </c>
+      <c r="BK47" t="n">
+        <v>146500</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>148520</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>121250</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="BT47" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="BU47" t="n">
+        <v>82.12</v>
+      </c>
+      <c r="BV47" t="n">
+        <v>102.38</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>84.81</v>
+      </c>
+      <c r="BY47" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="BZ47" t="n">
+        <v>146600</v>
+      </c>
+      <c r="CA47" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="CB47" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="CC47" t="n">
+        <v>121.18</v>
+      </c>
+      <c r="CE47" t="n">
+        <v>112.765</v>
+      </c>
+      <c r="CF47" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="CG47" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="CH47" t="n">
+        <v>32014.25</v>
+      </c>
+      <c r="CM47" t="n">
+        <v>59760</v>
+      </c>
+      <c r="CN47" t="n">
+        <v>29754.62</v>
+      </c>
+      <c r="CQ47" t="n">
+        <v>74140</v>
+      </c>
+      <c r="CS47" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="CT47" t="n">
+        <v>47281.86</v>
+      </c>
+      <c r="CU47" t="n">
+        <v>41575.111</v>
+      </c>
+      <c r="CV47" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="CW47" t="n">
+        <v>36128.597</v>
+      </c>
+      <c r="CX47" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="CY47" t="n">
+        <v>162300</v>
+      </c>
+      <c r="CZ47" t="n">
+        <v>170000</v>
+      </c>
+      <c r="DA47" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DB47" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="DC47" t="n">
+        <v>172990</v>
+      </c>
+      <c r="DD47" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="DE47" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="DF47" t="n">
+        <v>81.78</v>
+      </c>
+      <c r="DG47" t="n">
+        <v>125400</v>
+      </c>
+      <c r="DH47" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="DI47" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="DJ47" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="DK47" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="DL47" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="DM47" t="n">
+        <v>85.15000000000001</v>
+      </c>
+      <c r="DN47" t="n">
+        <v>51.35000000000001</v>
+      </c>
+      <c r="DO47" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="DP47" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DQ47" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="DR47" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="DS47" t="n">
+        <v>110</v>
+      </c>
+      <c r="DT47" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="DU47" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="DV47" t="n">
+        <v>110</v>
+      </c>
+      <c r="DW47" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="DX47" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DY47" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="DZ47" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="EA47" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="EB47" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="EC47" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="ED47" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="EE47" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="EF47" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="EG47" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="EH47" t="n">
+        <v>114.15</v>
+      </c>
+      <c r="EI47" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="EJ47" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="EK47" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="EL47" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EM47" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="EN47" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EO47" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="EP47" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="EQ47" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="ER47" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="ES47" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="ET47" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="EU47" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="EV47" t="n">
+        <v>103</v>
+      </c>
+      <c r="EW47" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="EX47" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="EY47" t="n">
+        <v>112</v>
+      </c>
+      <c r="EZ47" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="FA47" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="FB47" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="FC47" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="FD47" t="n">
+        <v>102</v>
+      </c>
+      <c r="FE47" t="n">
+        <v>112.15</v>
+      </c>
+      <c r="FF47" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="FG47" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="FH47" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="FI47" t="n">
+        <v>104</v>
+      </c>
+      <c r="FJ47" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="FK47" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="FL47" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="FM47" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="FN47" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="FO47" t="n">
+        <v>103</v>
+      </c>
+      <c r="FP47" t="n">
+        <v>110</v>
+      </c>
+      <c r="FQ47" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="FR47" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="FS47" t="n">
+        <v>103</v>
+      </c>
+      <c r="FT47" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="FU47" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="FV47" t="n">
+        <v>105</v>
+      </c>
+      <c r="FW47" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="FX47" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="FY47" t="n">
+        <v>106</v>
+      </c>
+      <c r="FZ47" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="GA47" t="n">
+        <v>102</v>
+      </c>
+      <c r="GB47" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GC47" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GD47" t="n">
+        <v>104</v>
+      </c>
+      <c r="GE47" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="GF47" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="GG47" t="n">
+        <v>100.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA47"/>
+  <dimension ref="A1:CA48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10474,6 +10474,223 @@
         <v>95.05</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>117.55</v>
+      </c>
+      <c r="G48" t="n">
+        <v>106.994</v>
+      </c>
+      <c r="H48" t="n">
+        <v>124.498</v>
+      </c>
+      <c r="I48" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="J48" t="n">
+        <v>127.95</v>
+      </c>
+      <c r="K48" t="n">
+        <v>119.835</v>
+      </c>
+      <c r="L48" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="N48" t="n">
+        <v>123.95</v>
+      </c>
+      <c r="O48" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="P48" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>112.85</v>
+      </c>
+      <c r="S48" t="n">
+        <v>167.25</v>
+      </c>
+      <c r="T48" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>217.65</v>
+      </c>
+      <c r="V48" t="n">
+        <v>120</v>
+      </c>
+      <c r="W48" t="n">
+        <v>387.85</v>
+      </c>
+      <c r="X48" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>271.5</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>347.2</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>118.35</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>148050</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>146900</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>126800</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>97</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>56.72000000000001</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>82.70999999999999</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>58.22999999999998</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>82.34</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>86.09000000000002</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>77.05</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>70.65000000000001</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>93.23999999999999</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>97.45</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>90.84999999999999</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>164.8</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>103.98</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>149780</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>147700</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>108</v>
+      </c>
+      <c r="BQ48" t="n">
+        <v>148600</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>121250</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>84.72</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>81.89</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="BW48" t="n">
+        <v>94.45</v>
+      </c>
+      <c r="BX48" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY48" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="BZ48" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA48" t="n">
+        <v>95.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG47"/>
+  <dimension ref="A1:GG48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -22436,6 +22436,529 @@
         <v>100.55</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>117.55</v>
+      </c>
+      <c r="G48" t="n">
+        <v>106.994</v>
+      </c>
+      <c r="H48" t="n">
+        <v>124.498</v>
+      </c>
+      <c r="I48" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="J48" t="n">
+        <v>127.95</v>
+      </c>
+      <c r="K48" t="n">
+        <v>119.835</v>
+      </c>
+      <c r="L48" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="N48" t="n">
+        <v>123.95</v>
+      </c>
+      <c r="O48" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="P48" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>112.85</v>
+      </c>
+      <c r="S48" t="n">
+        <v>167.25</v>
+      </c>
+      <c r="T48" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>217.65</v>
+      </c>
+      <c r="V48" t="n">
+        <v>120</v>
+      </c>
+      <c r="W48" t="n">
+        <v>387.85</v>
+      </c>
+      <c r="X48" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>271.5</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>347.2</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>118.35</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>148050</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>146900</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>126800</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>97</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>56.72000000000001</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>82.70999999999999</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>58.22999999999998</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>82.34</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>86.09000000000002</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>77.05</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>70.65000000000001</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>93.23999999999999</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>97.45</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>90.84999999999999</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>164.8</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>103.98</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>149780</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>147700</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>108</v>
+      </c>
+      <c r="BQ48" t="n">
+        <v>148600</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>121250</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>84.72</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>81.89</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="BW48" t="n">
+        <v>94.45</v>
+      </c>
+      <c r="BX48" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY48" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="BZ48" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA48" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="CB48" t="n">
+        <v>118.1</v>
+      </c>
+      <c r="CC48" t="n">
+        <v>121.247</v>
+      </c>
+      <c r="CE48" t="n">
+        <v>112.745</v>
+      </c>
+      <c r="CF48" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="CG48" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="CH48" t="n">
+        <v>32014.25</v>
+      </c>
+      <c r="CM48" t="n">
+        <v>59700</v>
+      </c>
+      <c r="CN48" t="n">
+        <v>29754.62</v>
+      </c>
+      <c r="CQ48" t="n">
+        <v>73800</v>
+      </c>
+      <c r="CS48" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="CT48" t="n">
+        <v>47281.86</v>
+      </c>
+      <c r="CU48" t="n">
+        <v>41575.111</v>
+      </c>
+      <c r="CV48" t="n">
+        <v>63.75999999999999</v>
+      </c>
+      <c r="CW48" t="n">
+        <v>36128.597</v>
+      </c>
+      <c r="CX48" t="n">
+        <v>171200</v>
+      </c>
+      <c r="CY48" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="CZ48" t="n">
+        <v>170300</v>
+      </c>
+      <c r="DA48" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="DB48" t="n">
+        <v>109</v>
+      </c>
+      <c r="DC48" t="n">
+        <v>171530</v>
+      </c>
+      <c r="DD48" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="DE48" t="n">
+        <v>79.65000000000001</v>
+      </c>
+      <c r="DF48" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="DG48" t="n">
+        <v>120140</v>
+      </c>
+      <c r="DH48" t="n">
+        <v>109</v>
+      </c>
+      <c r="DI48" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DJ48" t="n">
+        <v>109</v>
+      </c>
+      <c r="DK48" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="DL48" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="DM48" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="DN48" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="DO48" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="DP48" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DQ48" t="n">
+        <v>104</v>
+      </c>
+      <c r="DR48" t="n">
+        <v>112</v>
+      </c>
+      <c r="DS48" t="n">
+        <v>110</v>
+      </c>
+      <c r="DT48" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="DU48" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="DV48" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="DW48" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="DX48" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="DY48" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DZ48" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="EA48" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="EB48" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="EC48" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="ED48" t="n">
+        <v>112</v>
+      </c>
+      <c r="EE48" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="EF48" t="n">
+        <v>110</v>
+      </c>
+      <c r="EG48" t="n">
+        <v>93.13</v>
+      </c>
+      <c r="EH48" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="EI48" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="EJ48" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="EK48" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="EL48" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="EM48" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="EN48" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EO48" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="EP48" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="EQ48" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="ER48" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="ES48" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="ET48" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="EU48" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="EV48" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EW48" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="EX48" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="EY48" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="EZ48" t="n">
+        <v>105</v>
+      </c>
+      <c r="FA48" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="FB48" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="FC48" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="FD48" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="FE48" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="FF48" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="FG48" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="FH48" t="n">
+        <v>102</v>
+      </c>
+      <c r="FI48" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="FJ48" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="FK48" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="FL48" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="FM48" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="FN48" t="n">
+        <v>104</v>
+      </c>
+      <c r="FO48" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="FP48" t="n">
+        <v>110.85</v>
+      </c>
+      <c r="FQ48" t="n">
+        <v>102</v>
+      </c>
+      <c r="FR48" t="n">
+        <v>103</v>
+      </c>
+      <c r="FS48" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="FT48" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="FU48" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="FV48" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="FW48" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="FX48" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="FY48" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="FZ48" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="GA48" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="GB48" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="GC48" t="n">
+        <v>103</v>
+      </c>
+      <c r="GD48" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="GE48" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="GF48" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="GG48" t="n">
+        <v>100.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA48"/>
+  <dimension ref="A1:CA49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10691,6 +10691,223 @@
         <v>95.05</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>117.617</v>
+      </c>
+      <c r="G49" t="n">
+        <v>107.08</v>
+      </c>
+      <c r="H49" t="n">
+        <v>124.59</v>
+      </c>
+      <c r="I49" t="n">
+        <v>113.035</v>
+      </c>
+      <c r="J49" t="n">
+        <v>127.899</v>
+      </c>
+      <c r="K49" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="L49" t="n">
+        <v>144.695</v>
+      </c>
+      <c r="M49" t="n">
+        <v>131.47</v>
+      </c>
+      <c r="N49" t="n">
+        <v>123.85</v>
+      </c>
+      <c r="O49" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="P49" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>113.15</v>
+      </c>
+      <c r="S49" t="n">
+        <v>167.25</v>
+      </c>
+      <c r="T49" t="n">
+        <v>294.6</v>
+      </c>
+      <c r="U49" t="n">
+        <v>217.75</v>
+      </c>
+      <c r="V49" t="n">
+        <v>120.95</v>
+      </c>
+      <c r="W49" t="n">
+        <v>388.1</v>
+      </c>
+      <c r="X49" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>271.95</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>347.25</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>90.38</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>147700</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>146700</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>126730</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>97.82000000000001</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>81.98999999999999</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>58.09999999999999</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>82.16</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>76.95999999999999</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>70.47</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>103</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>93.53999999999999</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>90.84999999999999</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>104.13</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>149900</v>
+      </c>
+      <c r="BK49" t="n">
+        <v>146400</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>113.55</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>148400</v>
+      </c>
+      <c r="BR49" t="n">
+        <v>121200</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>91.72</v>
+      </c>
+      <c r="BT49" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="BU49" t="n">
+        <v>81.93000000000001</v>
+      </c>
+      <c r="BV49" t="n">
+        <v>102.34</v>
+      </c>
+      <c r="BW49" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="BX49" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="BY49" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="BZ49" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA49" t="n">
+        <v>94.90000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG48"/>
+  <dimension ref="A1:GG49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -22959,6 +22959,529 @@
         <v>100.75</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>117.617</v>
+      </c>
+      <c r="G49" t="n">
+        <v>107.08</v>
+      </c>
+      <c r="H49" t="n">
+        <v>124.59</v>
+      </c>
+      <c r="I49" t="n">
+        <v>113.035</v>
+      </c>
+      <c r="J49" t="n">
+        <v>127.899</v>
+      </c>
+      <c r="K49" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="L49" t="n">
+        <v>144.695</v>
+      </c>
+      <c r="M49" t="n">
+        <v>131.47</v>
+      </c>
+      <c r="N49" t="n">
+        <v>123.85</v>
+      </c>
+      <c r="O49" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="P49" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>113.15</v>
+      </c>
+      <c r="S49" t="n">
+        <v>167.25</v>
+      </c>
+      <c r="T49" t="n">
+        <v>294.6</v>
+      </c>
+      <c r="U49" t="n">
+        <v>217.75</v>
+      </c>
+      <c r="V49" t="n">
+        <v>120.95</v>
+      </c>
+      <c r="W49" t="n">
+        <v>388.1</v>
+      </c>
+      <c r="X49" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>271.95</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>347.25</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>90.38</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>147700</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>146700</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>126730</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>97.82000000000001</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>81.98999999999999</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>58.09999999999999</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>82.16</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>76.95999999999999</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>70.47</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>103</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>93.53999999999999</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>90.84999999999999</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>104.13</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>149900</v>
+      </c>
+      <c r="BK49" t="n">
+        <v>146400</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>113.55</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>148400</v>
+      </c>
+      <c r="BR49" t="n">
+        <v>121200</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>91.72</v>
+      </c>
+      <c r="BT49" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="BU49" t="n">
+        <v>81.93000000000001</v>
+      </c>
+      <c r="BV49" t="n">
+        <v>102.34</v>
+      </c>
+      <c r="BW49" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="BX49" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="BY49" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="BZ49" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA49" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="CB49" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="CC49" t="n">
+        <v>121.25</v>
+      </c>
+      <c r="CE49" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="CF49" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="CG49" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="CH49" t="n">
+        <v>32014.25</v>
+      </c>
+      <c r="CM49" t="n">
+        <v>59590</v>
+      </c>
+      <c r="CN49" t="n">
+        <v>29754.62</v>
+      </c>
+      <c r="CQ49" t="n">
+        <v>73000</v>
+      </c>
+      <c r="CS49" t="n">
+        <v>47.17000000000001</v>
+      </c>
+      <c r="CT49" t="n">
+        <v>47281.86</v>
+      </c>
+      <c r="CU49" t="n">
+        <v>41575.111</v>
+      </c>
+      <c r="CV49" t="n">
+        <v>64.28</v>
+      </c>
+      <c r="CW49" t="n">
+        <v>36128.597</v>
+      </c>
+      <c r="CX49" t="n">
+        <v>112.15</v>
+      </c>
+      <c r="CY49" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="CZ49" t="n">
+        <v>170300</v>
+      </c>
+      <c r="DA49" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="DB49" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="DC49" t="n">
+        <v>169200</v>
+      </c>
+      <c r="DD49" t="n">
+        <v>104</v>
+      </c>
+      <c r="DE49" t="n">
+        <v>79.64</v>
+      </c>
+      <c r="DF49" t="n">
+        <v>80.41</v>
+      </c>
+      <c r="DG49" t="n">
+        <v>119000</v>
+      </c>
+      <c r="DH49" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="DI49" t="n">
+        <v>108</v>
+      </c>
+      <c r="DJ49" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DK49" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="DL49" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="DM49" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="DN49" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="DO49" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="DP49" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="DQ49" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="DR49" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="DS49" t="n">
+        <v>110</v>
+      </c>
+      <c r="DT49" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DU49" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="DV49" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="DW49" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="DX49" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="DY49" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="DZ49" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="EA49" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="EB49" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="EC49" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="ED49" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="EE49" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="EF49" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="EG49" t="n">
+        <v>93.05999999999999</v>
+      </c>
+      <c r="EH49" t="n">
+        <v>114</v>
+      </c>
+      <c r="EI49" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="EJ49" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="EK49" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="EL49" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="EM49" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EN49" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="EO49" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="EP49" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="EQ49" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="ER49" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="ES49" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="ET49" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EU49" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="EV49" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EW49" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="EX49" t="n">
+        <v>108</v>
+      </c>
+      <c r="EY49" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="EZ49" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="FA49" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="FB49" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="FC49" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="FD49" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="FE49" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="FF49" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="FG49" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="FH49" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="FI49" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="FJ49" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="FK49" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="FL49" t="n">
+        <v>104</v>
+      </c>
+      <c r="FM49" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="FN49" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="FO49" t="n">
+        <v>103</v>
+      </c>
+      <c r="FP49" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="FQ49" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="FR49" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="FS49" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="FT49" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="FU49" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="FV49" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="FW49" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="FX49" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="FY49" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="FZ49" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="GA49" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="GB49" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="GC49" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GD49" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="GE49" t="n">
+        <v>106</v>
+      </c>
+      <c r="GF49" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="GG49" t="n">
+        <v>100.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -21651,9 +21651,6 @@
       <c r="CX46" t="n">
         <v>112.2</v>
       </c>
-      <c r="CY46" t="n">
-        <v>162680</v>
-      </c>
       <c r="CZ46" t="n">
         <v>169900</v>
       </c>
@@ -22174,9 +22171,6 @@
       <c r="CX47" t="n">
         <v>111.95</v>
       </c>
-      <c r="CY47" t="n">
-        <v>162300</v>
-      </c>
       <c r="CZ47" t="n">
         <v>170000</v>
       </c>
@@ -22693,9 +22687,6 @@
       </c>
       <c r="CW48" t="n">
         <v>36128.597</v>
-      </c>
-      <c r="CX48" t="n">
-        <v>171200</v>
       </c>
       <c r="CY48" t="n">
         <v>105.5</v>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA49"/>
+  <dimension ref="A1:CA50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10908,6 +10908,217 @@
         <v>94.90000000000001</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>107.089</v>
+      </c>
+      <c r="H50" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="I50" t="n">
+        <v>112.85</v>
+      </c>
+      <c r="J50" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>119.75</v>
+      </c>
+      <c r="L50" t="n">
+        <v>143.7</v>
+      </c>
+      <c r="M50" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>123.7</v>
+      </c>
+      <c r="O50" t="n">
+        <v>125.25</v>
+      </c>
+      <c r="P50" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="S50" t="n">
+        <v>167.2</v>
+      </c>
+      <c r="T50" t="n">
+        <v>294.05</v>
+      </c>
+      <c r="U50" t="n">
+        <v>217.15</v>
+      </c>
+      <c r="V50" t="n">
+        <v>120.55</v>
+      </c>
+      <c r="W50" t="n">
+        <v>387.4</v>
+      </c>
+      <c r="X50" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>271</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>98</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>345.55</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>93.98</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>127.15</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>118.05</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>147400</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>146300</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>125700</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>97</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>74.89</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>81.81999999999999</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>85.81999999999999</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>69.98</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>103</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>104.06</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>144990</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>147500</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>120000</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>84.48999999999999</v>
+      </c>
+      <c r="BU50" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="BV50" t="n">
+        <v>102.28</v>
+      </c>
+      <c r="BW50" t="n">
+        <v>94</v>
+      </c>
+      <c r="BX50" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="BY50" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="BZ50" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA50" t="n">
+        <v>94.29000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA50"/>
+  <dimension ref="A1:CA51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11119,6 +11119,217 @@
         <v>94.29000000000001</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>107.27</v>
+      </c>
+      <c r="H51" t="n">
+        <v>124.801</v>
+      </c>
+      <c r="I51" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>127.801</v>
+      </c>
+      <c r="K51" t="n">
+        <v>119.89</v>
+      </c>
+      <c r="L51" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="M51" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>123.59</v>
+      </c>
+      <c r="O51" t="n">
+        <v>125.44</v>
+      </c>
+      <c r="P51" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>113</v>
+      </c>
+      <c r="S51" t="n">
+        <v>167.45</v>
+      </c>
+      <c r="T51" t="n">
+        <v>294.7</v>
+      </c>
+      <c r="U51" t="n">
+        <v>217.45</v>
+      </c>
+      <c r="V51" t="n">
+        <v>121</v>
+      </c>
+      <c r="W51" t="n">
+        <v>387.5</v>
+      </c>
+      <c r="X51" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>271.4</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>347</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>94.19</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>127.399</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>147730</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>146750</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>126000</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>56.60000000000001</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>82.39</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>58.09999999999999</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>82.59</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>86.19</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>77.36</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>70.64</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>92.99000000000001</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>97.03</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>165.1</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="BK51" t="n">
+        <v>145500</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>113.85</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>148000</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>119800</v>
+      </c>
+      <c r="BS51" t="n">
+        <v>91.45</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>84.55</v>
+      </c>
+      <c r="BU51" t="n">
+        <v>81.72</v>
+      </c>
+      <c r="BV51" t="n">
+        <v>102.399</v>
+      </c>
+      <c r="BW51" t="n">
+        <v>96.73999999999999</v>
+      </c>
+      <c r="BX51" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="BY51" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ51" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA51" t="n">
+        <v>94.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -15,8 +15,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yy;@"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -47,9 +49,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -415,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG49"/>
+  <dimension ref="A1:GG51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -23473,6 +23476,958 @@
         <v>100.75</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="G50" t="n">
+        <v>107.089</v>
+      </c>
+      <c r="H50" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="I50" t="n">
+        <v>112.85</v>
+      </c>
+      <c r="J50" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>119.75</v>
+      </c>
+      <c r="L50" t="n">
+        <v>143.7</v>
+      </c>
+      <c r="M50" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>123.7</v>
+      </c>
+      <c r="O50" t="n">
+        <v>125.25</v>
+      </c>
+      <c r="P50" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="S50" t="n">
+        <v>167.2</v>
+      </c>
+      <c r="T50" t="n">
+        <v>294.05</v>
+      </c>
+      <c r="U50" t="n">
+        <v>217.15</v>
+      </c>
+      <c r="V50" t="n">
+        <v>120.55</v>
+      </c>
+      <c r="W50" t="n">
+        <v>387.4</v>
+      </c>
+      <c r="X50" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>271</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>98</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>345.55</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>93.98</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>127.15</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>118.05</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>147400</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>146300</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>125700</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>97</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>54.89999999999998</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>96.88999999999999</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>74.89</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>81.81999999999999</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>85.81999999999999</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>69.98</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>103</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>104.06</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>144990</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>147500</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>120000</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>84.48999999999999</v>
+      </c>
+      <c r="BU50" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="BV50" t="n">
+        <v>102.28</v>
+      </c>
+      <c r="BW50" t="n">
+        <v>94</v>
+      </c>
+      <c r="BX50" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="BY50" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="CA50" t="n">
+        <v>94.28999999999999</v>
+      </c>
+      <c r="CB50" t="n">
+        <v>117.65</v>
+      </c>
+      <c r="CC50" t="n">
+        <v>121.12</v>
+      </c>
+      <c r="CE50" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="CF50" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="CG50" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="CS50" t="n">
+        <v>47.99999999999999</v>
+      </c>
+      <c r="CV50" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="CX50" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="CY50" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="DA50" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="DB50" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="DD50" t="n">
+        <v>104</v>
+      </c>
+      <c r="DE50" t="n">
+        <v>79.47</v>
+      </c>
+      <c r="DF50" t="n">
+        <v>80.64</v>
+      </c>
+      <c r="DH50" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="DI50" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DJ50" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DK50" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="DL50" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="DM50" t="n">
+        <v>84.19</v>
+      </c>
+      <c r="DN50" t="n">
+        <v>51.25999999999999</v>
+      </c>
+      <c r="DO50" t="n">
+        <v>111</v>
+      </c>
+      <c r="DP50" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DQ50" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="DR50" t="n">
+        <v>111.65</v>
+      </c>
+      <c r="DS50" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="DT50" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DU50" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DV50" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="DW50" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="DX50" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="DY50" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="DZ50" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="EA50" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="EB50" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="EC50" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="ED50" t="n">
+        <v>111.65</v>
+      </c>
+      <c r="EE50" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="EF50" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="EG50" t="n">
+        <v>92.60999999999999</v>
+      </c>
+      <c r="EH50" t="n">
+        <v>114.15</v>
+      </c>
+      <c r="EI50" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="EJ50" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="EK50" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="EL50" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="EM50" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="EN50" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="EO50" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="EP50" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="EQ50" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="ER50" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="ES50" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="ET50" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="EU50" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="EV50" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="EW50" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="EX50" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="EY50" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="EZ50" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="FA50" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="FB50" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="FC50" t="n">
+        <v>106</v>
+      </c>
+      <c r="FD50" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="FE50" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="FF50" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="FG50" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="FH50" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="FI50" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="FJ50" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="FK50" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="FL50" t="n">
+        <v>104</v>
+      </c>
+      <c r="FM50" t="n">
+        <v>101</v>
+      </c>
+      <c r="FN50" t="n">
+        <v>101</v>
+      </c>
+      <c r="FO50" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="FP50" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="FQ50" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="FR50" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="FS50" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="FT50" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="FU50" t="n">
+        <v>100</v>
+      </c>
+      <c r="FV50" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="FW50" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="FX50" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="FY50" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="FZ50" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="GA50" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GB50" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="GC50" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="GD50" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="GE50" t="n">
+        <v>103.75</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="G51" t="n">
+        <v>107.27</v>
+      </c>
+      <c r="H51" t="n">
+        <v>124.801</v>
+      </c>
+      <c r="I51" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>127.801</v>
+      </c>
+      <c r="K51" t="n">
+        <v>119.89</v>
+      </c>
+      <c r="L51" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="M51" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>123.59</v>
+      </c>
+      <c r="O51" t="n">
+        <v>125.44</v>
+      </c>
+      <c r="P51" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>113</v>
+      </c>
+      <c r="S51" t="n">
+        <v>167.45</v>
+      </c>
+      <c r="T51" t="n">
+        <v>294.7</v>
+      </c>
+      <c r="U51" t="n">
+        <v>217.45</v>
+      </c>
+      <c r="V51" t="n">
+        <v>121</v>
+      </c>
+      <c r="W51" t="n">
+        <v>387.5</v>
+      </c>
+      <c r="X51" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>271.4</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>347</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>94.19</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>127.399</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>147730</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>146750</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>126000</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>56.60000000000001</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>82.39</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>58.09999999999999</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>82.59</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>86.19</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>77.36</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>70.64</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>92.99000000000001</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>97.03</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>165.1</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="BK51" t="n">
+        <v>145500</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>113.85</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>148000</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>119800</v>
+      </c>
+      <c r="BS51" t="n">
+        <v>91.45</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>84.55</v>
+      </c>
+      <c r="BU51" t="n">
+        <v>81.72</v>
+      </c>
+      <c r="BV51" t="n">
+        <v>102.399</v>
+      </c>
+      <c r="BW51" t="n">
+        <v>96.73999999999999</v>
+      </c>
+      <c r="BX51" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="BY51" t="n">
+        <v>104</v>
+      </c>
+      <c r="CA51" t="n">
+        <v>94.55</v>
+      </c>
+      <c r="CB51" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="CC51" t="n">
+        <v>121.4</v>
+      </c>
+      <c r="CE51" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="CF51" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="CG51" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="CS51" t="n">
+        <v>49.00000000000001</v>
+      </c>
+      <c r="CV51" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="CX51" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="DA51" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="DB51" t="n">
+        <v>104</v>
+      </c>
+      <c r="DD51" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="DE51" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="DF51" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="DH51" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="DI51" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="DJ51" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="DK51" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="DL51" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="DM51" t="n">
+        <v>84.02</v>
+      </c>
+      <c r="DN51" t="n">
+        <v>51.46000000000001</v>
+      </c>
+      <c r="DO51" t="n">
+        <v>110.85</v>
+      </c>
+      <c r="DP51" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DQ51" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="DR51" t="n">
+        <v>112</v>
+      </c>
+      <c r="DS51" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DT51" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DU51" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DV51" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="DW51" t="n">
+        <v>112</v>
+      </c>
+      <c r="DX51" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DY51" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="DZ51" t="n">
+        <v>113</v>
+      </c>
+      <c r="EA51" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="EB51" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="EC51" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="ED51" t="n">
+        <v>111.55</v>
+      </c>
+      <c r="EE51" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="EF51" t="n">
+        <v>110</v>
+      </c>
+      <c r="EG51" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="EH51" t="n">
+        <v>114.45</v>
+      </c>
+      <c r="EI51" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="EJ51" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="EK51" t="n">
+        <v>111</v>
+      </c>
+      <c r="EL51" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="EM51" t="n">
+        <v>107</v>
+      </c>
+      <c r="EN51" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="EO51" t="n">
+        <v>109</v>
+      </c>
+      <c r="EP51" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="EQ51" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="ER51" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="ES51" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="ET51" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EU51" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="EV51" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="EW51" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="EX51" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="EY51" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="EZ51" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="FA51" t="n">
+        <v>104</v>
+      </c>
+      <c r="FB51" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="FC51" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="FD51" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="FE51" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="FF51" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="FG51" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="FH51" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="FI51" t="n">
+        <v>104</v>
+      </c>
+      <c r="FJ51" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="FK51" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="FL51" t="n">
+        <v>104</v>
+      </c>
+      <c r="FM51" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="FN51" t="n">
+        <v>104</v>
+      </c>
+      <c r="FO51" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="FP51" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="FQ51" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="FR51" t="n">
+        <v>103</v>
+      </c>
+      <c r="FS51" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="FT51" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="FU51" t="n">
+        <v>100</v>
+      </c>
+      <c r="FV51" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="FW51" t="n">
+        <v>104</v>
+      </c>
+      <c r="FX51" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="FY51" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="FZ51" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="GA51" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="GB51" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GC51" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="GD51" t="n">
+        <v>104</v>
+      </c>
+      <c r="GE51" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="GG51" t="n">
+        <v>100.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA51"/>
+  <dimension ref="A1:CA52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11330,6 +11330,217 @@
         <v>94.55</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="H52" t="n">
+        <v>124.855</v>
+      </c>
+      <c r="I52" t="n">
+        <v>113.22</v>
+      </c>
+      <c r="J52" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="K52" t="n">
+        <v>120.14</v>
+      </c>
+      <c r="L52" t="n">
+        <v>144.86</v>
+      </c>
+      <c r="M52" t="n">
+        <v>131.38</v>
+      </c>
+      <c r="N52" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="O52" t="n">
+        <v>125.58</v>
+      </c>
+      <c r="P52" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>113.65</v>
+      </c>
+      <c r="S52" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="T52" t="n">
+        <v>294.9</v>
+      </c>
+      <c r="U52" t="n">
+        <v>217.35</v>
+      </c>
+      <c r="V52" t="n">
+        <v>120.4</v>
+      </c>
+      <c r="W52" t="n">
+        <v>388</v>
+      </c>
+      <c r="X52" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>270.8</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>346.7</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>93.98999999999999</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>127.55</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>118.55</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>104</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>147920</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>147590</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>126700</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>97.14000000000001</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>96.91</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>80.14</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>82.89</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>75.15000000000001</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>87.05999999999999</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>77.86</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>70.88</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>93.26000000000001</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>97.04000000000001</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>165.3</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>104.363</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>146000</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>107</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>148500</v>
+      </c>
+      <c r="BR52" t="n">
+        <v>120400</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>91.48</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="BU52" t="n">
+        <v>81.73</v>
+      </c>
+      <c r="BV52" t="n">
+        <v>102.585</v>
+      </c>
+      <c r="BW52" t="n">
+        <v>94.34999999999999</v>
+      </c>
+      <c r="BX52" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="BY52" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="BZ52" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA52" t="n">
+        <v>94.59999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -15,10 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yy;@"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,10 +48,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG51"/>
+  <dimension ref="A1:GP52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1370,6 +1370,51 @@
           <t>WBS3D</t>
         </is>
       </c>
+      <c r="GH1" t="inlineStr">
+        <is>
+          <t>S16O6</t>
+        </is>
+      </c>
+      <c r="GI1" t="inlineStr">
+        <is>
+          <t>D15E7</t>
+        </is>
+      </c>
+      <c r="GJ1" t="inlineStr">
+        <is>
+          <t>TMVE8</t>
+        </is>
+      </c>
+      <c r="GK1" t="inlineStr">
+        <is>
+          <t>ICC6D</t>
+        </is>
+      </c>
+      <c r="GL1" t="inlineStr">
+        <is>
+          <t>VSCZD</t>
+        </is>
+      </c>
+      <c r="GM1" t="inlineStr">
+        <is>
+          <t>NPCED</t>
+        </is>
+      </c>
+      <c r="GN1" t="inlineStr">
+        <is>
+          <t>OZC8D</t>
+        </is>
+      </c>
+      <c r="GO1" t="inlineStr">
+        <is>
+          <t>LQC1D</t>
+        </is>
+      </c>
+      <c r="GP1" t="inlineStr">
+        <is>
+          <t>MR44D</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -23477,7 +23522,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="G50" t="n">
@@ -23953,7 +23998,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>46234</v>
       </c>
       <c r="G51" t="n">
@@ -24426,6 +24471,541 @@
       </c>
       <c r="GG51" t="n">
         <v>100.6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="H52" t="n">
+        <v>124.855</v>
+      </c>
+      <c r="I52" t="n">
+        <v>113.22</v>
+      </c>
+      <c r="J52" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="K52" t="n">
+        <v>120.14</v>
+      </c>
+      <c r="L52" t="n">
+        <v>144.86</v>
+      </c>
+      <c r="M52" t="n">
+        <v>131.38</v>
+      </c>
+      <c r="N52" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="O52" t="n">
+        <v>125.58</v>
+      </c>
+      <c r="P52" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>113.65</v>
+      </c>
+      <c r="S52" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="T52" t="n">
+        <v>294.9</v>
+      </c>
+      <c r="U52" t="n">
+        <v>217.35</v>
+      </c>
+      <c r="V52" t="n">
+        <v>120.4</v>
+      </c>
+      <c r="W52" t="n">
+        <v>388</v>
+      </c>
+      <c r="X52" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>270.8</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>346.7</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>93.98999999999999</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>127.55</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>118.55</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>104</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>147920</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>147590</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>126700</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>97.14000000000001</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>96.91</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>80.14</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>82.89</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>75.15000000000001</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>87.05999999999999</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>77.86</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>70.88</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>93.26000000000001</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>97.04000000000001</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>165.3</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>104.363</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>146000</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>107</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>148500</v>
+      </c>
+      <c r="BR52" t="n">
+        <v>120400</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>91.48</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="BU52" t="n">
+        <v>81.73</v>
+      </c>
+      <c r="BV52" t="n">
+        <v>102.585</v>
+      </c>
+      <c r="BW52" t="n">
+        <v>94.34999999999999</v>
+      </c>
+      <c r="BX52" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="BY52" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="BZ52" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA52" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="CB52" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="CC52" t="n">
+        <v>121.37</v>
+      </c>
+      <c r="CE52" t="n">
+        <v>113</v>
+      </c>
+      <c r="CF52" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="CG52" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="CH52" t="n">
+        <v>32014.25</v>
+      </c>
+      <c r="CM52" t="n">
+        <v>59300</v>
+      </c>
+      <c r="CN52" t="n">
+        <v>29754.62</v>
+      </c>
+      <c r="CQ52" t="n">
+        <v>74410</v>
+      </c>
+      <c r="CS52" t="n">
+        <v>47.61</v>
+      </c>
+      <c r="CT52" t="n">
+        <v>47281.86</v>
+      </c>
+      <c r="CU52" t="n">
+        <v>41575.111</v>
+      </c>
+      <c r="CV52" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="CW52" t="n">
+        <v>36128.597</v>
+      </c>
+      <c r="CX52" t="n">
+        <v>112</v>
+      </c>
+      <c r="CY52" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="CZ52" t="n">
+        <v>168240</v>
+      </c>
+      <c r="DA52" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="DB52" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="DC52" t="n">
+        <v>168890</v>
+      </c>
+      <c r="DD52" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="DE52" t="n">
+        <v>80.22</v>
+      </c>
+      <c r="DF52" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="DG52" t="n">
+        <v>120000</v>
+      </c>
+      <c r="DH52" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DI52" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DJ52" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="DK52" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="DL52" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="DM52" t="n">
+        <v>84.34999999999999</v>
+      </c>
+      <c r="DN52" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="DO52" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="DP52" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DQ52" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="DR52" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="DS52" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="DT52" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DU52" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="DV52" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="DW52" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="DX52" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="DY52" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="DZ52" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="EA52" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="EB52" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="EC52" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="ED52" t="n">
+        <v>112</v>
+      </c>
+      <c r="EE52" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="EF52" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="EG52" t="n">
+        <v>93.20000000000002</v>
+      </c>
+      <c r="EH52" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="EI52" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="EJ52" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="EK52" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="EL52" t="n">
+        <v>106</v>
+      </c>
+      <c r="EM52" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="EN52" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EO52" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="EP52" t="n">
+        <v>110</v>
+      </c>
+      <c r="EQ52" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="ER52" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="ES52" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="ET52" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EU52" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="EV52" t="n">
+        <v>104</v>
+      </c>
+      <c r="EW52" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="EX52" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="EY52" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="EZ52" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="FA52" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="FB52" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="FC52" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="FD52" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="FE52" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="FF52" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="FG52" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="FH52" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="FI52" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="FJ52" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="FK52" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="FL52" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="FM52" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="FN52" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="FO52" t="n">
+        <v>103</v>
+      </c>
+      <c r="FP52" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="FQ52" t="n">
+        <v>102</v>
+      </c>
+      <c r="FR52" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="FS52" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="FT52" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="FU52" t="n">
+        <v>99.89999999999999</v>
+      </c>
+      <c r="FV52" t="n">
+        <v>105</v>
+      </c>
+      <c r="FW52" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="FX52" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="FY52" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="FZ52" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="GA52" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GB52" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GC52" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="GD52" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="GE52" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="GH52" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="GI52" t="n">
+        <v>148000</v>
+      </c>
+      <c r="GJ52" t="n">
+        <v>136500</v>
+      </c>
+      <c r="GL52" t="n">
+        <v>100</v>
+      </c>
+      <c r="GM52" t="n">
+        <v>100</v>
+      </c>
+      <c r="GN52" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="GO52" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GP52" t="n">
+        <v>25.499</v>
       </c>
     </row>
   </sheetData>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA52"/>
+  <dimension ref="A1:CA53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11541,6 +11541,217 @@
         <v>94.59999999999999</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>107.412</v>
+      </c>
+      <c r="H53" t="n">
+        <v>125.08</v>
+      </c>
+      <c r="I53" t="n">
+        <v>113.29</v>
+      </c>
+      <c r="J53" t="n">
+        <v>127.92</v>
+      </c>
+      <c r="K53" t="n">
+        <v>120.15</v>
+      </c>
+      <c r="L53" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="M53" t="n">
+        <v>131.3</v>
+      </c>
+      <c r="N53" t="n">
+        <v>123.749</v>
+      </c>
+      <c r="O53" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="P53" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="S53" t="n">
+        <v>167.8</v>
+      </c>
+      <c r="T53" t="n">
+        <v>294.95</v>
+      </c>
+      <c r="U53" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="V53" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="W53" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="X53" t="n">
+        <v>104</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>270.5</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>346.4</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>93.84999999999999</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>127.65</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>112.95</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>107</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>147910</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>147140</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>126330</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>97.34999999999998</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>96.68999999999998</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>56.18</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>87.09999999999998</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>77.79000000000001</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>92.61</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>90.44</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>146500</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="BQ53" t="n">
+        <v>148450</v>
+      </c>
+      <c r="BR53" t="n">
+        <v>120600</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="BU53" t="n">
+        <v>81.69</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>102.59</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="BY53" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>94.65000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GP52"/>
+  <dimension ref="A1:GP53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -25008,6 +25008,259 @@
         <v>25.499</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>107.412</v>
+      </c>
+      <c r="H53" t="n">
+        <v>125.08</v>
+      </c>
+      <c r="I53" t="n">
+        <v>113.29</v>
+      </c>
+      <c r="J53" t="n">
+        <v>127.92</v>
+      </c>
+      <c r="K53" t="n">
+        <v>120.15</v>
+      </c>
+      <c r="L53" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="M53" t="n">
+        <v>131.3</v>
+      </c>
+      <c r="N53" t="n">
+        <v>123.749</v>
+      </c>
+      <c r="O53" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="P53" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="S53" t="n">
+        <v>167.8</v>
+      </c>
+      <c r="T53" t="n">
+        <v>294.95</v>
+      </c>
+      <c r="U53" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="V53" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="W53" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="X53" t="n">
+        <v>104</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>270.5</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>346.4</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>93.84999999999999</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>127.65</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>112.95</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>107</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>147910</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>147140</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>126330</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>96.69</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>56.18</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>77.79000000000001</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>92.61</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>90.44</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>146500</v>
+      </c>
+      <c r="BQ53" t="n">
+        <v>148450</v>
+      </c>
+      <c r="BR53" t="n">
+        <v>120600</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="BU53" t="n">
+        <v>81.69</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>102.59</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="BY53" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="CB53" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="CC53" t="n">
+        <v>121.451</v>
+      </c>
+      <c r="CE53" t="n">
+        <v>113.103</v>
+      </c>
+      <c r="CF53" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="CG53" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="CH53" t="n">
+        <v>32014.25</v>
+      </c>
+      <c r="CM53" t="n">
+        <v>58560</v>
+      </c>
+      <c r="CN53" t="n">
+        <v>29754.62</v>
+      </c>
+      <c r="CQ53" t="n">
+        <v>73900</v>
+      </c>
+      <c r="CT53" t="n">
+        <v>47281.86</v>
+      </c>
+      <c r="CU53" t="n">
+        <v>41575.111</v>
+      </c>
+      <c r="CW53" t="n">
+        <v>36128.597</v>
+      </c>
+      <c r="CZ53" t="n">
+        <v>167870</v>
+      </c>
+      <c r="DC53" t="n">
+        <v>167400</v>
+      </c>
+      <c r="DG53" t="n">
+        <v>119980</v>
+      </c>
+      <c r="GH53" t="n">
+        <v>100.369</v>
+      </c>
+      <c r="GI53" t="n">
+        <v>147890</v>
+      </c>
+      <c r="GJ53" t="n">
+        <v>136700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA53"/>
+  <dimension ref="A1:CA54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11752,6 +11752,217 @@
         <v>94.65000000000001</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>107.48</v>
+      </c>
+      <c r="H54" t="n">
+        <v>125.12</v>
+      </c>
+      <c r="I54" t="n">
+        <v>113.28</v>
+      </c>
+      <c r="J54" t="n">
+        <v>128.049</v>
+      </c>
+      <c r="K54" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>144.207</v>
+      </c>
+      <c r="M54" t="n">
+        <v>131.176</v>
+      </c>
+      <c r="N54" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="O54" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="P54" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>113.45</v>
+      </c>
+      <c r="S54" t="n">
+        <v>167.55</v>
+      </c>
+      <c r="T54" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>217</v>
+      </c>
+      <c r="V54" t="n">
+        <v>119.65</v>
+      </c>
+      <c r="W54" t="n">
+        <v>387.9</v>
+      </c>
+      <c r="X54" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>270.05</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>346</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>93.55</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>89</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>127.65</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>118</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>106</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>147900</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>146800</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>126400</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>96.44</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>56.89999999999999</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>75.34999999999999</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>58.38</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>82.59</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>92.61</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="BK54" t="n">
+        <v>145710</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="BQ54" t="n">
+        <v>148500</v>
+      </c>
+      <c r="BR54" t="n">
+        <v>120190</v>
+      </c>
+      <c r="BS54" t="n">
+        <v>90.84999999999999</v>
+      </c>
+      <c r="BT54" t="n">
+        <v>83.98999999999999</v>
+      </c>
+      <c r="BU54" t="n">
+        <v>81.04000000000001</v>
+      </c>
+      <c r="BV54" t="n">
+        <v>102.579</v>
+      </c>
+      <c r="BW54" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="BX54" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="BY54" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="BZ54" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA54" t="n">
+        <v>94.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA54"/>
+  <dimension ref="A1:CA55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11963,6 +11963,217 @@
         <v>94.52</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>107.56</v>
+      </c>
+      <c r="H55" t="n">
+        <v>125.18</v>
+      </c>
+      <c r="I55" t="n">
+        <v>113.39</v>
+      </c>
+      <c r="J55" t="n">
+        <v>127.8</v>
+      </c>
+      <c r="K55" t="n">
+        <v>120.05</v>
+      </c>
+      <c r="L55" t="n">
+        <v>144.24</v>
+      </c>
+      <c r="M55" t="n">
+        <v>131</v>
+      </c>
+      <c r="N55" t="n">
+        <v>123.249</v>
+      </c>
+      <c r="O55" t="n">
+        <v>125.05</v>
+      </c>
+      <c r="P55" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="S55" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="T55" t="n">
+        <v>295.05</v>
+      </c>
+      <c r="U55" t="n">
+        <v>216.8</v>
+      </c>
+      <c r="V55" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="W55" t="n">
+        <v>388</v>
+      </c>
+      <c r="X55" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>98</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>344.8</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>127.78</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>148100</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>148000</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>126600</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>96.70999999999999</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>54.70999999999999</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>81.34999999999999</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>74.29000000000001</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>55.77000000000001</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>81.70999999999999</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>85.65000000000001</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>76.31</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>92.34999999999998</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>104.49</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>147300</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>148700</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>120280</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="BT55" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="BU55" t="n">
+        <v>80.84</v>
+      </c>
+      <c r="BV55" t="n">
+        <v>102.48</v>
+      </c>
+      <c r="BW55" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="BX55" t="n">
+        <v>83.05</v>
+      </c>
+      <c r="BY55" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="BZ55" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA55" t="n">
+        <v>94.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA55"/>
+  <dimension ref="A1:CA56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -12174,6 +12174,217 @@
         <v>94.25</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>107.829</v>
+      </c>
+      <c r="H56" t="n">
+        <v>125.46</v>
+      </c>
+      <c r="I56" t="n">
+        <v>113.69</v>
+      </c>
+      <c r="J56" t="n">
+        <v>128.31</v>
+      </c>
+      <c r="K56" t="n">
+        <v>120.3</v>
+      </c>
+      <c r="L56" t="n">
+        <v>144.4</v>
+      </c>
+      <c r="M56" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="N56" t="n">
+        <v>123.45</v>
+      </c>
+      <c r="O56" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="P56" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>113</v>
+      </c>
+      <c r="S56" t="n">
+        <v>168.6</v>
+      </c>
+      <c r="T56" t="n">
+        <v>296.35</v>
+      </c>
+      <c r="U56" t="n">
+        <v>218.8</v>
+      </c>
+      <c r="V56" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="W56" t="n">
+        <v>388.35</v>
+      </c>
+      <c r="X56" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>272.5</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>347.85</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>94.23999999999999</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>128.24</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>118.85</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>114</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>148110</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>148700</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>126480</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>96.55</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>54.40000000000001</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>80.27</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>55.50000000000001</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>81.06</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>75.51000000000001</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>69.45</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>92.50000000000001</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>98</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>104.839</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>146800</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>148650</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>120450</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="BT56" t="n">
+        <v>84.45</v>
+      </c>
+      <c r="BU56" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="BV56" t="n">
+        <v>102.725</v>
+      </c>
+      <c r="BW56" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="BX56" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="BY56" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="BZ56" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA56" t="n">
+        <v>94.10000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA56"/>
+  <dimension ref="A1:CA57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -12385,6 +12385,217 @@
         <v>94.10000000000001</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>107.895</v>
+      </c>
+      <c r="H57" t="n">
+        <v>125.575</v>
+      </c>
+      <c r="I57" t="n">
+        <v>113.82</v>
+      </c>
+      <c r="J57" t="n">
+        <v>128.45</v>
+      </c>
+      <c r="K57" t="n">
+        <v>120.375</v>
+      </c>
+      <c r="L57" t="n">
+        <v>144.451</v>
+      </c>
+      <c r="M57" t="n">
+        <v>131</v>
+      </c>
+      <c r="N57" t="n">
+        <v>123.25</v>
+      </c>
+      <c r="O57" t="n">
+        <v>125.3</v>
+      </c>
+      <c r="P57" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="S57" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="T57" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>218.75</v>
+      </c>
+      <c r="V57" t="n">
+        <v>120.55</v>
+      </c>
+      <c r="W57" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="X57" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>272.5</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>347.6</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>90.12</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>128.3</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>119.05</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>114.65</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>147690</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>149010</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>126200</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>54.40000000000001</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>95.15000000000001</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>56.43</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>80.34</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>57.99999999999999</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>84.86</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>76.01000000000001</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>69</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>93.01000000000001</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>166.25</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>104.89</v>
+      </c>
+      <c r="BK57" t="n">
+        <v>146500</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>113.65</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="BQ57" t="n">
+        <v>148400</v>
+      </c>
+      <c r="BR57" t="n">
+        <v>120300</v>
+      </c>
+      <c r="BS57" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="BT57" t="n">
+        <v>84.45</v>
+      </c>
+      <c r="BU57" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="BV57" t="n">
+        <v>102.899</v>
+      </c>
+      <c r="BW57" t="n">
+        <v>94.84999999999999</v>
+      </c>
+      <c r="BX57" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="BY57" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="BZ57" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA57" t="n">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA57"/>
+  <dimension ref="A1:CA58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -12596,6 +12596,217 @@
         <v>94</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>107.96</v>
+      </c>
+      <c r="H58" t="n">
+        <v>125.605</v>
+      </c>
+      <c r="I58" t="n">
+        <v>113.885</v>
+      </c>
+      <c r="J58" t="n">
+        <v>128.53</v>
+      </c>
+      <c r="K58" t="n">
+        <v>120.551</v>
+      </c>
+      <c r="L58" t="n">
+        <v>144.55</v>
+      </c>
+      <c r="M58" t="n">
+        <v>131.15</v>
+      </c>
+      <c r="N58" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>125.3</v>
+      </c>
+      <c r="P58" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="S58" t="n">
+        <v>169</v>
+      </c>
+      <c r="T58" t="n">
+        <v>297.85</v>
+      </c>
+      <c r="U58" t="n">
+        <v>219.15</v>
+      </c>
+      <c r="V58" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="W58" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="X58" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>272.65</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>347</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>94.23</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>90.15000000000001</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>128.35</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>107</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>104</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>148100</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>149000</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>126290</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>96.20999999999999</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>54.45</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>77.61</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>80.29000000000001</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>56.11999999999999</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>58.35999999999999</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>84.66</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>75.56999999999999</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>93.29000000000001</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="BI58" t="n">
+        <v>104.91</v>
+      </c>
+      <c r="BK58" t="n">
+        <v>146700</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="BQ58" t="n">
+        <v>148400</v>
+      </c>
+      <c r="BR58" t="n">
+        <v>120300</v>
+      </c>
+      <c r="BS58" t="n">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="BT58" t="n">
+        <v>84.55</v>
+      </c>
+      <c r="BU58" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="BV58" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="BW58" t="n">
+        <v>94.76000000000001</v>
+      </c>
+      <c r="BX58" t="n">
+        <v>84.89</v>
+      </c>
+      <c r="BY58" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="BZ58" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA58" t="n">
+        <v>93.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA58"/>
+  <dimension ref="A1:CA59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -12807,6 +12807,214 @@
         <v>93.69</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>125.759</v>
+      </c>
+      <c r="I59" t="n">
+        <v>113.89</v>
+      </c>
+      <c r="J59" t="n">
+        <v>128.749</v>
+      </c>
+      <c r="K59" t="n">
+        <v>120.73</v>
+      </c>
+      <c r="L59" t="n">
+        <v>144.65</v>
+      </c>
+      <c r="M59" t="n">
+        <v>131.13</v>
+      </c>
+      <c r="N59" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="O59" t="n">
+        <v>125.85</v>
+      </c>
+      <c r="P59" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>111</v>
+      </c>
+      <c r="S59" t="n">
+        <v>169.3</v>
+      </c>
+      <c r="T59" t="n">
+        <v>297.4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>219.45</v>
+      </c>
+      <c r="V59" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="W59" t="n">
+        <v>387.8</v>
+      </c>
+      <c r="X59" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>272.75</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>346.75</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>94.13</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>89.83</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>128.47</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>119.15</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>147850</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>148000</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>126260</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>54.50000000000001</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>94.69</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>80.12</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>72</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>56.03</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>81.11</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>84.52</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>75.70999999999999</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>69.56999999999999</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>93.04000000000001</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>90.23</v>
+      </c>
+      <c r="BH59" t="n">
+        <v>166.45</v>
+      </c>
+      <c r="BI59" t="n">
+        <v>104.99</v>
+      </c>
+      <c r="BK59" t="n">
+        <v>146990</v>
+      </c>
+      <c r="BM59" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>108</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>114</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="BQ59" t="n">
+        <v>148350</v>
+      </c>
+      <c r="BR59" t="n">
+        <v>119990</v>
+      </c>
+      <c r="BS59" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="BT59" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="BU59" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="BV59" t="n">
+        <v>103.088</v>
+      </c>
+      <c r="BW59" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="BX59" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="BY59" t="n">
+        <v>105</v>
+      </c>
+      <c r="BZ59" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA59" t="n">
+        <v>93.65000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA59"/>
+  <dimension ref="A1:CA60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -13015,6 +13015,214 @@
         <v>93.65000000000001</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>126</v>
+      </c>
+      <c r="I60" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>128.92</v>
+      </c>
+      <c r="K60" t="n">
+        <v>121.045</v>
+      </c>
+      <c r="L60" t="n">
+        <v>145.3</v>
+      </c>
+      <c r="M60" t="n">
+        <v>131.451</v>
+      </c>
+      <c r="N60" t="n">
+        <v>123.88</v>
+      </c>
+      <c r="O60" t="n">
+        <v>125.84</v>
+      </c>
+      <c r="P60" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>111.55</v>
+      </c>
+      <c r="S60" t="n">
+        <v>169.65</v>
+      </c>
+      <c r="T60" t="n">
+        <v>297.95</v>
+      </c>
+      <c r="U60" t="n">
+        <v>219.5</v>
+      </c>
+      <c r="V60" t="n">
+        <v>120.75</v>
+      </c>
+      <c r="W60" t="n">
+        <v>388.9</v>
+      </c>
+      <c r="X60" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>273.15</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>347.1</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>90</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>128.7</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>119.25</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>147750</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>147500</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>125800</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>95.77</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>54.42</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>93.93000000000001</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>71.42</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>80.89</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>75.31999999999999</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>69</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>97</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>90.06</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>166.8</v>
+      </c>
+      <c r="BI60" t="n">
+        <v>105.24</v>
+      </c>
+      <c r="BK60" t="n">
+        <v>145600</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>113.85</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="BQ60" t="n">
+        <v>148380</v>
+      </c>
+      <c r="BR60" t="n">
+        <v>120000</v>
+      </c>
+      <c r="BS60" t="n">
+        <v>91.48999999999999</v>
+      </c>
+      <c r="BT60" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="BU60" t="n">
+        <v>80.95</v>
+      </c>
+      <c r="BV60" t="n">
+        <v>103.22</v>
+      </c>
+      <c r="BW60" t="n">
+        <v>95</v>
+      </c>
+      <c r="BX60" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY60" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="BZ60" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA60" t="n">
+        <v>93.48999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA60"/>
+  <dimension ref="A1:CA61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -13223,6 +13223,214 @@
         <v>93.48999999999999</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>126</v>
+      </c>
+      <c r="I61" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>128.92</v>
+      </c>
+      <c r="K61" t="n">
+        <v>121.045</v>
+      </c>
+      <c r="L61" t="n">
+        <v>145.3</v>
+      </c>
+      <c r="M61" t="n">
+        <v>131.451</v>
+      </c>
+      <c r="N61" t="n">
+        <v>123.88</v>
+      </c>
+      <c r="O61" t="n">
+        <v>125.84</v>
+      </c>
+      <c r="P61" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>111.55</v>
+      </c>
+      <c r="S61" t="n">
+        <v>169.65</v>
+      </c>
+      <c r="T61" t="n">
+        <v>297.95</v>
+      </c>
+      <c r="U61" t="n">
+        <v>219.5</v>
+      </c>
+      <c r="V61" t="n">
+        <v>120.75</v>
+      </c>
+      <c r="W61" t="n">
+        <v>388.9</v>
+      </c>
+      <c r="X61" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>273.15</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>347.1</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>90</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>128.7</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>119.25</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>147750</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>147500</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>125800</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>95.77</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>54.42</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>93.93000000000001</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>71.42</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>80.89</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>75.31999999999999</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>69</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>97</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>90.06</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>166.8</v>
+      </c>
+      <c r="BI61" t="n">
+        <v>105.24</v>
+      </c>
+      <c r="BK61" t="n">
+        <v>145600</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>113.85</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="BQ61" t="n">
+        <v>148380</v>
+      </c>
+      <c r="BR61" t="n">
+        <v>120000</v>
+      </c>
+      <c r="BS61" t="n">
+        <v>91.48999999999999</v>
+      </c>
+      <c r="BT61" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="BU61" t="n">
+        <v>80.95</v>
+      </c>
+      <c r="BV61" t="n">
+        <v>103.22</v>
+      </c>
+      <c r="BW61" t="n">
+        <v>95</v>
+      </c>
+      <c r="BX61" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY61" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="BZ61" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA61" t="n">
+        <v>93.48999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA61"/>
+  <dimension ref="A1:CA62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -13431,6 +13431,214 @@
         <v>93.48999999999999</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>126.04</v>
+      </c>
+      <c r="I62" t="n">
+        <v>113.993</v>
+      </c>
+      <c r="J62" t="n">
+        <v>128.51</v>
+      </c>
+      <c r="K62" t="n">
+        <v>120.36</v>
+      </c>
+      <c r="L62" t="n">
+        <v>144.65</v>
+      </c>
+      <c r="M62" t="n">
+        <v>130.25</v>
+      </c>
+      <c r="N62" t="n">
+        <v>122.51</v>
+      </c>
+      <c r="O62" t="n">
+        <v>125.45</v>
+      </c>
+      <c r="P62" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="S62" t="n">
+        <v>169.25</v>
+      </c>
+      <c r="T62" t="n">
+        <v>297.05</v>
+      </c>
+      <c r="U62" t="n">
+        <v>217.9</v>
+      </c>
+      <c r="V62" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="W62" t="n">
+        <v>385</v>
+      </c>
+      <c r="X62" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>272.65</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>344</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>118.05</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>148000</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>146610</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>126280</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>102</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>94.80000000000001</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>53.67000000000001</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>55.74</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>78.15000000000001</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>70.47</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>74</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>67</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>96</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="BH62" t="n">
+        <v>166.75</v>
+      </c>
+      <c r="BI62" t="n">
+        <v>105.063</v>
+      </c>
+      <c r="BK62" t="n">
+        <v>146460</v>
+      </c>
+      <c r="BM62" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="BN62" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="BO62" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="BP62" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="BQ62" t="n">
+        <v>149110</v>
+      </c>
+      <c r="BR62" t="n">
+        <v>120000</v>
+      </c>
+      <c r="BS62" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="BT62" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="BU62" t="n">
+        <v>80.05</v>
+      </c>
+      <c r="BV62" t="n">
+        <v>102.965</v>
+      </c>
+      <c r="BW62" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="BX62" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY62" t="n">
+        <v>105</v>
+      </c>
+      <c r="BZ62" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA62" t="n">
+        <v>91.73999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA62"/>
+  <dimension ref="A1:CA63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -13639,6 +13639,214 @@
         <v>91.73999999999999</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="I63" t="n">
+        <v>113.99</v>
+      </c>
+      <c r="J63" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="L63" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="M63" t="n">
+        <v>129.67</v>
+      </c>
+      <c r="N63" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="O63" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="P63" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="S63" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="T63" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="U63" t="n">
+        <v>217.25</v>
+      </c>
+      <c r="V63" t="n">
+        <v>120</v>
+      </c>
+      <c r="W63" t="n">
+        <v>384.05</v>
+      </c>
+      <c r="X63" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>270</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>98.48999999999999</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>342.75</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>89.09</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>128.825</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>118.65</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>113</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>148350</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>146600</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>124740</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>102</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>94.25999999999999</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>53.45</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>92.62</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>55.40999999999999</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>77.97</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>57.22000000000001</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>79.23999999999999</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>73.84999999999999</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>92.30000000000001</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>166.8</v>
+      </c>
+      <c r="BI63" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="BK63" t="n">
+        <v>146400</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>102</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>113.45</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="BQ63" t="n">
+        <v>149100</v>
+      </c>
+      <c r="BR63" t="n">
+        <v>117700</v>
+      </c>
+      <c r="BS63" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="BT63" t="n">
+        <v>82.55</v>
+      </c>
+      <c r="BU63" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="BV63" t="n">
+        <v>102.865</v>
+      </c>
+      <c r="BW63" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="BX63" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="BY63" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="BZ63" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA63" t="n">
+        <v>91.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA63"/>
+  <dimension ref="A1:CA64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -13847,6 +13847,214 @@
         <v>91.25</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>126.236</v>
+      </c>
+      <c r="I64" t="n">
+        <v>114.28</v>
+      </c>
+      <c r="J64" t="n">
+        <v>128.814</v>
+      </c>
+      <c r="K64" t="n">
+        <v>120.98</v>
+      </c>
+      <c r="L64" t="n">
+        <v>145.1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>131.54</v>
+      </c>
+      <c r="N64" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="O64" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="P64" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="S64" t="n">
+        <v>169.4</v>
+      </c>
+      <c r="T64" t="n">
+        <v>296.9</v>
+      </c>
+      <c r="U64" t="n">
+        <v>218.35</v>
+      </c>
+      <c r="V64" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="W64" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="X64" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>271</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>344.2</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>129</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>119.45</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>148500</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>147050</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>124000</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>93.89</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>92</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>68.87</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>55.67999999999999</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>78.06</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>82.45</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>72.92</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>67</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>91</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="BH64" t="n">
+        <v>167.2</v>
+      </c>
+      <c r="BI64" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="BK64" t="n">
+        <v>146000</v>
+      </c>
+      <c r="BM64" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="BN64" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="BO64" t="n">
+        <v>113.65</v>
+      </c>
+      <c r="BP64" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="BQ64" t="n">
+        <v>149200</v>
+      </c>
+      <c r="BR64" t="n">
+        <v>119000</v>
+      </c>
+      <c r="BS64" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="BT64" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="BU64" t="n">
+        <v>80.58</v>
+      </c>
+      <c r="BV64" t="n">
+        <v>103.34</v>
+      </c>
+      <c r="BW64" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="BX64" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="BY64" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="BZ64" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA64" t="n">
+        <v>90.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA64"/>
+  <dimension ref="A1:CA65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -14055,6 +14055,214 @@
         <v>90.75</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>126.492</v>
+      </c>
+      <c r="I65" t="n">
+        <v>114.64</v>
+      </c>
+      <c r="J65" t="n">
+        <v>129.306</v>
+      </c>
+      <c r="K65" t="n">
+        <v>121.435</v>
+      </c>
+      <c r="L65" t="n">
+        <v>145.7</v>
+      </c>
+      <c r="M65" t="n">
+        <v>131.94</v>
+      </c>
+      <c r="N65" t="n">
+        <v>124.35</v>
+      </c>
+      <c r="O65" t="n">
+        <v>126</v>
+      </c>
+      <c r="P65" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="S65" t="n">
+        <v>169.85</v>
+      </c>
+      <c r="T65" t="n">
+        <v>297.9</v>
+      </c>
+      <c r="U65" t="n">
+        <v>219.1</v>
+      </c>
+      <c r="V65" t="n">
+        <v>120.95</v>
+      </c>
+      <c r="W65" t="n">
+        <v>386.25</v>
+      </c>
+      <c r="X65" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>272.25</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>96.45999999999999</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>345.9</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>93.86</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>129.31</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>148800</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>146750</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>123590</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>53.34999999999999</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>92.29999999999998</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>75.29000000000001</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>78.18000000000001</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>69.95999999999999</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>55.93</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>57.00999999999999</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>79.89</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>92</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>96.45999999999999</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>167.4</v>
+      </c>
+      <c r="BI65" t="n">
+        <v>105.63</v>
+      </c>
+      <c r="BK65" t="n">
+        <v>146000</v>
+      </c>
+      <c r="BM65" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>113.45</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>108</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>149550</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>117400</v>
+      </c>
+      <c r="BS65" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="BT65" t="n">
+        <v>83.95</v>
+      </c>
+      <c r="BU65" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="BV65" t="n">
+        <v>103.56</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="BY65" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="BZ65" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA65" t="n">
+        <v>91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA65"/>
+  <dimension ref="A1:CA66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -14263,6 +14263,214 @@
         <v>91</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>126.575</v>
+      </c>
+      <c r="I66" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="J66" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="K66" t="n">
+        <v>121.52</v>
+      </c>
+      <c r="L66" t="n">
+        <v>146.08</v>
+      </c>
+      <c r="M66" t="n">
+        <v>132.34</v>
+      </c>
+      <c r="N66" t="n">
+        <v>124.63</v>
+      </c>
+      <c r="O66" t="n">
+        <v>126</v>
+      </c>
+      <c r="P66" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>110</v>
+      </c>
+      <c r="S66" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="T66" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="U66" t="n">
+        <v>219.2</v>
+      </c>
+      <c r="V66" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="W66" t="n">
+        <v>387.5</v>
+      </c>
+      <c r="X66" t="n">
+        <v>105</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>272.45</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>98.34999999999999</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>345.7</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>93.84</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>116</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>149650</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>147500</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>125360</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>94.34</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>92.59000000000002</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>55.16</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>75.18000000000001</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>55.89999999999999</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>57.10000000000001</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>79.66</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>83.65000000000001</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>74.41</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>67.95999999999999</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>91.40000000000002</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>167.8</v>
+      </c>
+      <c r="BI66" t="n">
+        <v>105.769</v>
+      </c>
+      <c r="BK66" t="n">
+        <v>147390</v>
+      </c>
+      <c r="BM66" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>150550</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>119010</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="BT66" t="n">
+        <v>84</v>
+      </c>
+      <c r="BU66" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="BV66" t="n">
+        <v>103.717</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>91.11000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA66"/>
+  <dimension ref="A1:CA67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -14471,6 +14471,214 @@
         <v>91.11000000000001</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>126.677</v>
+      </c>
+      <c r="I67" t="n">
+        <v>114.82</v>
+      </c>
+      <c r="J67" t="n">
+        <v>129.31</v>
+      </c>
+      <c r="K67" t="n">
+        <v>121.44</v>
+      </c>
+      <c r="L67" t="n">
+        <v>145.652</v>
+      </c>
+      <c r="M67" t="n">
+        <v>132.19</v>
+      </c>
+      <c r="N67" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="O67" t="n">
+        <v>125.34</v>
+      </c>
+      <c r="P67" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="S67" t="n">
+        <v>170.05</v>
+      </c>
+      <c r="T67" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="U67" t="n">
+        <v>219.4</v>
+      </c>
+      <c r="V67" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="W67" t="n">
+        <v>388.15</v>
+      </c>
+      <c r="X67" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>272.5</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>345.4</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>93.94</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>89.13</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>129.495</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>120.15</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>115.15</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>104</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>149900</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>147800</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>125640</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>94.42</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>53.67999999999999</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>92.99000000000001</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>55.11000000000001</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>75.09</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>70</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>57.46999999999999</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>79.61</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>67.78</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>91.88999999999999</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>96.66</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="BI67" t="n">
+        <v>105.805</v>
+      </c>
+      <c r="BK67" t="n">
+        <v>147000</v>
+      </c>
+      <c r="BM67" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="BQ67" t="n">
+        <v>150650</v>
+      </c>
+      <c r="BR67" t="n">
+        <v>119100</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="BT67" t="n">
+        <v>83.94</v>
+      </c>
+      <c r="BU67" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="BV67" t="n">
+        <v>103.72</v>
+      </c>
+      <c r="BW67" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="BX67" t="n">
+        <v>84.12</v>
+      </c>
+      <c r="BY67" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="BZ67" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA67" t="n">
+        <v>90.90000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA67"/>
+  <dimension ref="A1:CA68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -14679,6 +14679,214 @@
         <v>90.90000000000001</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>126.768</v>
+      </c>
+      <c r="I68" t="n">
+        <v>114.864</v>
+      </c>
+      <c r="J68" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="K68" t="n">
+        <v>121.475</v>
+      </c>
+      <c r="L68" t="n">
+        <v>145.45</v>
+      </c>
+      <c r="M68" t="n">
+        <v>131.945</v>
+      </c>
+      <c r="N68" t="n">
+        <v>124.15</v>
+      </c>
+      <c r="O68" t="n">
+        <v>125.345</v>
+      </c>
+      <c r="P68" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="S68" t="n">
+        <v>170.1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="U68" t="n">
+        <v>219.25</v>
+      </c>
+      <c r="V68" t="n">
+        <v>121.45</v>
+      </c>
+      <c r="W68" t="n">
+        <v>388.05</v>
+      </c>
+      <c r="X68" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>272.6</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>345.95</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>94</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>129.58</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>120.35</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>107</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>150210</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>147860</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>125850</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>94.34999999999999</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>53.41</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>55.05</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>75</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>78.05</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>55.72000000000001</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>79.56999999999999</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>83.86</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>74.02</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>68.03</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>91.77</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>91.27</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="BI68" t="n">
+        <v>105.855</v>
+      </c>
+      <c r="BK68" t="n">
+        <v>147200</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="BQ68" t="n">
+        <v>151010</v>
+      </c>
+      <c r="BR68" t="n">
+        <v>119110</v>
+      </c>
+      <c r="BS68" t="n">
+        <v>91.48999999999999</v>
+      </c>
+      <c r="BT68" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="BU68" t="n">
+        <v>81.19</v>
+      </c>
+      <c r="BV68" t="n">
+        <v>103.869</v>
+      </c>
+      <c r="BW68" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="BX68" t="n">
+        <v>84.73999999999999</v>
+      </c>
+      <c r="BY68" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="BZ68" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA68" t="n">
+        <v>90.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA68"/>
+  <dimension ref="A1:CA69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -14887,6 +14887,214 @@
         <v>90.94</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>126.816</v>
+      </c>
+      <c r="I69" t="n">
+        <v>114.92</v>
+      </c>
+      <c r="J69" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="K69" t="n">
+        <v>121.57</v>
+      </c>
+      <c r="L69" t="n">
+        <v>145.75</v>
+      </c>
+      <c r="M69" t="n">
+        <v>131.93</v>
+      </c>
+      <c r="N69" t="n">
+        <v>123.99</v>
+      </c>
+      <c r="O69" t="n">
+        <v>125.42</v>
+      </c>
+      <c r="P69" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="S69" t="n">
+        <v>170.2</v>
+      </c>
+      <c r="T69" t="n">
+        <v>298.4</v>
+      </c>
+      <c r="U69" t="n">
+        <v>219.5</v>
+      </c>
+      <c r="V69" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="W69" t="n">
+        <v>388.8</v>
+      </c>
+      <c r="X69" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>272.75</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>345.95</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>94</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>129.655</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>149950</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>147800</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>125880</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>78.55</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>70.70999999999999</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>55.99</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>57.71</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>79.84999999999999</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>67.95999999999999</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>105.91</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>147100</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="BQ69" t="n">
+        <v>151100</v>
+      </c>
+      <c r="BR69" t="n">
+        <v>119450</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="BU69" t="n">
+        <v>81.44</v>
+      </c>
+      <c r="BV69" t="n">
+        <v>103.914</v>
+      </c>
+      <c r="BW69" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="BX69" t="n">
+        <v>84.69</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>91.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA69"/>
+  <dimension ref="A1:CA70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -15095,6 +15095,205 @@
         <v>91.12</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>115.234</v>
+      </c>
+      <c r="J70" t="n">
+        <v>130.022</v>
+      </c>
+      <c r="K70" t="n">
+        <v>121.88</v>
+      </c>
+      <c r="L70" t="n">
+        <v>146.45</v>
+      </c>
+      <c r="M70" t="n">
+        <v>132.59</v>
+      </c>
+      <c r="N70" t="n">
+        <v>124.45</v>
+      </c>
+      <c r="O70" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="S70" t="n">
+        <v>170.75</v>
+      </c>
+      <c r="T70" t="n">
+        <v>299.35</v>
+      </c>
+      <c r="U70" t="n">
+        <v>220.25</v>
+      </c>
+      <c r="V70" t="n">
+        <v>121.65</v>
+      </c>
+      <c r="W70" t="n">
+        <v>389.5</v>
+      </c>
+      <c r="X70" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>273</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>345.95</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>94</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>89</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>150360</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>147390</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>125970</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>94.48</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>53.90000000000001</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>75.52</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>78.20999999999999</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>57.79999999999999</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>79.86</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>83.84</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>97.86</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>91</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>168.65</v>
+      </c>
+      <c r="BI70" t="n">
+        <v>106.185</v>
+      </c>
+      <c r="BK70" t="n">
+        <v>147500</v>
+      </c>
+      <c r="BM70" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="BN70" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>114.95</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>108</v>
+      </c>
+      <c r="BR70" t="n">
+        <v>119950</v>
+      </c>
+      <c r="BS70" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="BT70" t="n">
+        <v>85</v>
+      </c>
+      <c r="BU70" t="n">
+        <v>81.84999999999999</v>
+      </c>
+      <c r="BV70" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="BW70" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="BX70" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="BY70" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="BZ70" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA70" t="n">
+        <v>90.05999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA70"/>
+  <dimension ref="A1:CA71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -15294,6 +15294,205 @@
         <v>90.05999999999999</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>115.43</v>
+      </c>
+      <c r="J71" t="n">
+        <v>130.237</v>
+      </c>
+      <c r="K71" t="n">
+        <v>122.12</v>
+      </c>
+      <c r="L71" t="n">
+        <v>146.94</v>
+      </c>
+      <c r="M71" t="n">
+        <v>132.77</v>
+      </c>
+      <c r="N71" t="n">
+        <v>124.85</v>
+      </c>
+      <c r="O71" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="P71" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="S71" t="n">
+        <v>170.9</v>
+      </c>
+      <c r="T71" t="n">
+        <v>299.8</v>
+      </c>
+      <c r="U71" t="n">
+        <v>220.4</v>
+      </c>
+      <c r="V71" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="W71" t="n">
+        <v>389.65</v>
+      </c>
+      <c r="X71" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>273.3</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>346.6</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>121.15</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>115.25</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>150350</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>147300</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>125600</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>76</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>78.44</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>70.37</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>55.63000000000001</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>57.60999999999999</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>79.48</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>73.87</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>92.42</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>168.75</v>
+      </c>
+      <c r="BI71" t="n">
+        <v>106.271</v>
+      </c>
+      <c r="BK71" t="n">
+        <v>147400</v>
+      </c>
+      <c r="BM71" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="BN71" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="BO71" t="n">
+        <v>114.45</v>
+      </c>
+      <c r="BP71" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="BR71" t="n">
+        <v>119170</v>
+      </c>
+      <c r="BS71" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="BT71" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="BU71" t="n">
+        <v>82.18000000000001</v>
+      </c>
+      <c r="BV71" t="n">
+        <v>104.39</v>
+      </c>
+      <c r="BW71" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="BX71" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="BY71" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="BZ71" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA71" t="n">
+        <v>90.19999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA71"/>
+  <dimension ref="A1:CA72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -15493,6 +15493,205 @@
         <v>90.19999999999999</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>115.455</v>
+      </c>
+      <c r="J72" t="n">
+        <v>130.29</v>
+      </c>
+      <c r="K72" t="n">
+        <v>122.265</v>
+      </c>
+      <c r="L72" t="n">
+        <v>147.3</v>
+      </c>
+      <c r="M72" t="n">
+        <v>133.05</v>
+      </c>
+      <c r="N72" t="n">
+        <v>124.99</v>
+      </c>
+      <c r="O72" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="P72" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>111</v>
+      </c>
+      <c r="S72" t="n">
+        <v>171.15</v>
+      </c>
+      <c r="T72" t="n">
+        <v>300</v>
+      </c>
+      <c r="U72" t="n">
+        <v>220.9</v>
+      </c>
+      <c r="V72" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="W72" t="n">
+        <v>391.7</v>
+      </c>
+      <c r="X72" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>274</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>347.3</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>94.29000000000001</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>89.89</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>121.3</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>116</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>150400</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>147790</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>125510</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>94.83</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>92.36</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>78.54000000000001</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>57.94</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>73.93000000000001</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>68.09</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>92.97</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="BI72" t="n">
+        <v>106.331</v>
+      </c>
+      <c r="BK72" t="n">
+        <v>147500</v>
+      </c>
+      <c r="BM72" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="BN72" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="BO72" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="BP72" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="BR72" t="n">
+        <v>119400</v>
+      </c>
+      <c r="BS72" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="BT72" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="BU72" t="n">
+        <v>82.34999999999999</v>
+      </c>
+      <c r="BV72" t="n">
+        <v>104.498</v>
+      </c>
+      <c r="BW72" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="BX72" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="BY72" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="BZ72" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA72" t="n">
+        <v>90.54000000000002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA72"/>
+  <dimension ref="A1:CA73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -15692,6 +15692,205 @@
         <v>90.54000000000002</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>115.545</v>
+      </c>
+      <c r="J73" t="n">
+        <v>130.45</v>
+      </c>
+      <c r="K73" t="n">
+        <v>122.38</v>
+      </c>
+      <c r="L73" t="n">
+        <v>147.199</v>
+      </c>
+      <c r="M73" t="n">
+        <v>133.25</v>
+      </c>
+      <c r="N73" t="n">
+        <v>125.25</v>
+      </c>
+      <c r="O73" t="n">
+        <v>126.55</v>
+      </c>
+      <c r="P73" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="S73" t="n">
+        <v>171.25</v>
+      </c>
+      <c r="T73" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="U73" t="n">
+        <v>221.6</v>
+      </c>
+      <c r="V73" t="n">
+        <v>121.95</v>
+      </c>
+      <c r="W73" t="n">
+        <v>393.55</v>
+      </c>
+      <c r="X73" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>274.5</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>348.3</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>94.48</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>115.55</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>150320</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>147600</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>125100</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>94.28</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>55.67999999999999</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>71</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>57.49999999999999</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>83.68000000000001</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>74.18000000000001</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>93.00000000000001</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>92.48999999999999</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="BF73" t="n">
+        <v>92</v>
+      </c>
+      <c r="BH73" t="n">
+        <v>168.95</v>
+      </c>
+      <c r="BI73" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="BK73" t="n">
+        <v>147480</v>
+      </c>
+      <c r="BM73" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="BN73" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="BO73" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="BP73" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="BR73" t="n">
+        <v>119190</v>
+      </c>
+      <c r="BS73" t="n">
+        <v>93</v>
+      </c>
+      <c r="BT73" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="BU73" t="n">
+        <v>82.55</v>
+      </c>
+      <c r="BV73" t="n">
+        <v>104.53</v>
+      </c>
+      <c r="BW73" t="n">
+        <v>96.34999999999999</v>
+      </c>
+      <c r="BX73" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY73" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="BZ73" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA73" t="n">
+        <v>90.18000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA73"/>
+  <dimension ref="A1:CA74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -15891,6 +15891,205 @@
         <v>90.18000000000001</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>115.62</v>
+      </c>
+      <c r="J74" t="n">
+        <v>130.45</v>
+      </c>
+      <c r="K74" t="n">
+        <v>122.489</v>
+      </c>
+      <c r="L74" t="n">
+        <v>147.38</v>
+      </c>
+      <c r="M74" t="n">
+        <v>133.35</v>
+      </c>
+      <c r="N74" t="n">
+        <v>125.53</v>
+      </c>
+      <c r="O74" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="P74" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>111</v>
+      </c>
+      <c r="S74" t="n">
+        <v>171.45</v>
+      </c>
+      <c r="T74" t="n">
+        <v>301.4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="V74" t="n">
+        <v>122.35</v>
+      </c>
+      <c r="W74" t="n">
+        <v>395.6</v>
+      </c>
+      <c r="X74" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>276.25</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>350.25</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>90.19</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>121.55</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>117.85</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>150050</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>147700</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>125100</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>54.31</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>55.82</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>78.81</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>71.26000000000001</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>83.88</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>68.48999999999999</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>93.20000000000002</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>93.23</v>
+      </c>
+      <c r="BE74" t="n">
+        <v>99</v>
+      </c>
+      <c r="BF74" t="n">
+        <v>92.03</v>
+      </c>
+      <c r="BH74" t="n">
+        <v>169.1</v>
+      </c>
+      <c r="BI74" t="n">
+        <v>106.485</v>
+      </c>
+      <c r="BK74" t="n">
+        <v>147580</v>
+      </c>
+      <c r="BM74" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="BN74" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="BO74" t="n">
+        <v>113.85</v>
+      </c>
+      <c r="BP74" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="BR74" t="n">
+        <v>119000</v>
+      </c>
+      <c r="BS74" t="n">
+        <v>93</v>
+      </c>
+      <c r="BT74" t="n">
+        <v>85.65000000000001</v>
+      </c>
+      <c r="BU74" t="n">
+        <v>82.55</v>
+      </c>
+      <c r="BV74" t="n">
+        <v>104.63</v>
+      </c>
+      <c r="BW74" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="BX74" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="BY74" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ74" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA74" t="n">
+        <v>90.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA74"/>
+  <dimension ref="A1:CA75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -16090,6 +16090,205 @@
         <v>90.69</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>115.82</v>
+      </c>
+      <c r="J75" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="K75" t="n">
+        <v>122.77</v>
+      </c>
+      <c r="L75" t="n">
+        <v>147.67</v>
+      </c>
+      <c r="M75" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="N75" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="O75" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="P75" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>171.8</v>
+      </c>
+      <c r="T75" t="n">
+        <v>302</v>
+      </c>
+      <c r="U75" t="n">
+        <v>223</v>
+      </c>
+      <c r="V75" t="n">
+        <v>123</v>
+      </c>
+      <c r="W75" t="n">
+        <v>395.3</v>
+      </c>
+      <c r="X75" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>277.2</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>352</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>95.48999999999999</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>90.53</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>150190</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>147500</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>125000</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>94.93000000000002</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>54.40000000000001</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>76.98</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>56.13</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>58.09999999999999</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>80.11</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>84.23999999999999</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>74.68000000000001</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>93.36</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>169.38</v>
+      </c>
+      <c r="BI75" t="n">
+        <v>106.675</v>
+      </c>
+      <c r="BK75" t="n">
+        <v>147540</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>101</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>114.45</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>118850</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>85.89</v>
+      </c>
+      <c r="BU75" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="BV75" t="n">
+        <v>104.84</v>
+      </c>
+      <c r="BW75" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="BY75" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="BZ75" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA75" t="n">
+        <v>90.58999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA75"/>
+  <dimension ref="A1:CA76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -16289,6 +16289,205 @@
         <v>90.58999999999999</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="J76" t="n">
+        <v>130.9</v>
+      </c>
+      <c r="K76" t="n">
+        <v>122.9</v>
+      </c>
+      <c r="L76" t="n">
+        <v>147.7</v>
+      </c>
+      <c r="M76" t="n">
+        <v>133.72</v>
+      </c>
+      <c r="N76" t="n">
+        <v>125.803</v>
+      </c>
+      <c r="O76" t="n">
+        <v>126.901</v>
+      </c>
+      <c r="P76" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>111.05</v>
+      </c>
+      <c r="S76" t="n">
+        <v>172</v>
+      </c>
+      <c r="T76" t="n">
+        <v>302.3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>223.3</v>
+      </c>
+      <c r="V76" t="n">
+        <v>123</v>
+      </c>
+      <c r="W76" t="n">
+        <v>395.75</v>
+      </c>
+      <c r="X76" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>277.35</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>115.7</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>150420</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>148000</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>125300</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>54.28999999999999</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>92.76000000000002</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>77</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>79.06999999999999</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>71.31</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>58.32000000000001</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>83.86</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>74.55</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>68.73999999999999</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>93.42</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="BF76" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="BH76" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="BI76" t="n">
+        <v>106.737</v>
+      </c>
+      <c r="BK76" t="n">
+        <v>147800</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="BR76" t="n">
+        <v>118650</v>
+      </c>
+      <c r="BS76" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="BT76" t="n">
+        <v>86.05</v>
+      </c>
+      <c r="BU76" t="n">
+        <v>82.95</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>104.93</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>85.34999999999999</v>
+      </c>
+      <c r="BY76" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="BZ76" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA76" t="n">
+        <v>90.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA76"/>
+  <dimension ref="A1:CA77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -16488,6 +16488,205 @@
         <v>90.8</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>115.978</v>
+      </c>
+      <c r="J77" t="n">
+        <v>130.993</v>
+      </c>
+      <c r="K77" t="n">
+        <v>122.89</v>
+      </c>
+      <c r="L77" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="M77" t="n">
+        <v>133.75</v>
+      </c>
+      <c r="N77" t="n">
+        <v>125.75</v>
+      </c>
+      <c r="O77" t="n">
+        <v>127.05</v>
+      </c>
+      <c r="P77" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="S77" t="n">
+        <v>172.15</v>
+      </c>
+      <c r="T77" t="n">
+        <v>302.5</v>
+      </c>
+      <c r="U77" t="n">
+        <v>223.35</v>
+      </c>
+      <c r="V77" t="n">
+        <v>123</v>
+      </c>
+      <c r="W77" t="n">
+        <v>397.15</v>
+      </c>
+      <c r="X77" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>277.6</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>352.4</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>150510</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>147880</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>124600</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>95.07000000000001</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>54.40999999999999</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>92.91</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>55.91</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>76.55</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>71.26000000000001</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>84.13</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>74.88</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>68.92</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>93.45</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>169.625</v>
+      </c>
+      <c r="BI77" t="n">
+        <v>106.81</v>
+      </c>
+      <c r="BK77" t="n">
+        <v>147600</v>
+      </c>
+      <c r="BM77" t="n">
+        <v>101</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>101</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>114.45</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="BR77" t="n">
+        <v>118000</v>
+      </c>
+      <c r="BS77" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="BT77" t="n">
+        <v>86</v>
+      </c>
+      <c r="BU77" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="BV77" t="n">
+        <v>104.981</v>
+      </c>
+      <c r="BW77" t="n">
+        <v>97</v>
+      </c>
+      <c r="BX77" t="n">
+        <v>84.91</v>
+      </c>
+      <c r="BY77" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="BZ77" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA77" t="n">
+        <v>90.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA77"/>
+  <dimension ref="A1:CA78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -16687,6 +16687,205 @@
         <v>90.84</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>116.09</v>
+      </c>
+      <c r="J78" t="n">
+        <v>131.049</v>
+      </c>
+      <c r="K78" t="n">
+        <v>122.84</v>
+      </c>
+      <c r="L78" t="n">
+        <v>147.59</v>
+      </c>
+      <c r="M78" t="n">
+        <v>133.751</v>
+      </c>
+      <c r="N78" t="n">
+        <v>125.81</v>
+      </c>
+      <c r="O78" t="n">
+        <v>126.85</v>
+      </c>
+      <c r="P78" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="S78" t="n">
+        <v>172.05</v>
+      </c>
+      <c r="T78" t="n">
+        <v>302.2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>223.25</v>
+      </c>
+      <c r="V78" t="n">
+        <v>123</v>
+      </c>
+      <c r="W78" t="n">
+        <v>397</v>
+      </c>
+      <c r="X78" t="n">
+        <v>107</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>277.55</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>352.3</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>121.85</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>115.85</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>150750</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>147650</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>125050</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>94.97000000000001</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>92.69999999999999</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>56.07</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>76.56</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>79.04000000000001</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>56.00999999999999</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>58.25000000000001</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>84.13</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>68.52</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>93.18999999999998</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>169.72</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>106.898</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>147800</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>108</v>
+      </c>
+      <c r="BR78" t="n">
+        <v>118150</v>
+      </c>
+      <c r="BS78" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="BT78" t="n">
+        <v>86.06</v>
+      </c>
+      <c r="BU78" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="BV78" t="n">
+        <v>105</v>
+      </c>
+      <c r="BW78" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="BX78" t="n">
+        <v>85.75</v>
+      </c>
+      <c r="BY78" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="BZ78" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA78" t="n">
+        <v>90.82999999999998</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA78"/>
+  <dimension ref="A1:CA79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -16886,6 +16886,205 @@
         <v>90.82999999999998</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>116.13</v>
+      </c>
+      <c r="J79" t="n">
+        <v>131.17</v>
+      </c>
+      <c r="K79" t="n">
+        <v>123.037</v>
+      </c>
+      <c r="L79" t="n">
+        <v>148.04</v>
+      </c>
+      <c r="M79" t="n">
+        <v>134</v>
+      </c>
+      <c r="N79" t="n">
+        <v>126.05</v>
+      </c>
+      <c r="O79" t="n">
+        <v>127.25</v>
+      </c>
+      <c r="P79" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="S79" t="n">
+        <v>172.302</v>
+      </c>
+      <c r="T79" t="n">
+        <v>302.5</v>
+      </c>
+      <c r="U79" t="n">
+        <v>223.25</v>
+      </c>
+      <c r="V79" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="W79" t="n">
+        <v>396.5</v>
+      </c>
+      <c r="X79" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>277.9</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>95.55</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>90</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>115.85</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>150750</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>146450</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>125390</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>54.47000000000001</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>92.35000000000001</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>76</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>56.35999999999999</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>58.09000000000001</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>74.06999999999999</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>104</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>92.95</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>92.56999999999999</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="BI79" t="n">
+        <v>106.965</v>
+      </c>
+      <c r="BK79" t="n">
+        <v>147100</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>113.95</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>118720</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>93.88</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>86.34</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>83.39</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>90.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA79"/>
+  <dimension ref="A1:CA80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -17085,6 +17085,205 @@
         <v>90.63</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>116.33</v>
+      </c>
+      <c r="J80" t="n">
+        <v>131.35</v>
+      </c>
+      <c r="K80" t="n">
+        <v>123.29</v>
+      </c>
+      <c r="L80" t="n">
+        <v>148.3</v>
+      </c>
+      <c r="M80" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="N80" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="O80" t="n">
+        <v>127.499</v>
+      </c>
+      <c r="P80" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="S80" t="n">
+        <v>172.74</v>
+      </c>
+      <c r="T80" t="n">
+        <v>304.25</v>
+      </c>
+      <c r="U80" t="n">
+        <v>223.3</v>
+      </c>
+      <c r="V80" t="n">
+        <v>123</v>
+      </c>
+      <c r="W80" t="n">
+        <v>397.05</v>
+      </c>
+      <c r="X80" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>278.35</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>352.8</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>122</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>116.05</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>109</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>150600</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>146550</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>125490</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>94.62</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>54.56999999999999</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>92.44</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>55.69</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>70.04000000000001</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>56.41</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>58.17000000000001</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>104</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>93.08</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>93.20999999999999</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>170.173</v>
+      </c>
+      <c r="BI80" t="n">
+        <v>107.151</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>147200</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>114.15</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>118600</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>94.11</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>83.41</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>105.28</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>90.34999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
